--- a/news_daily/2026-08-16.xlsx
+++ b/news_daily/2026-08-16.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -84,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -93,9 +88,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1078,32 +1070,32 @@
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -1147,7 +1139,7 @@
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -1156,7 +1148,11 @@
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>43157c9cfb53448ea716cfae1dedba42</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>be6948fe80f28d89445238d5</t>
@@ -1179,7 +1175,7 @@
       <c r="AN3" s="2" t="inlineStr"/>
       <c r="AO3" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP3" s="2" t="inlineStr"/>
@@ -1221,10 +1217,22 @@
       </c>
       <c r="BG3" s="2" t="inlineStr"/>
       <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2008,32 +2016,32 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2077,7 +2085,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -2086,7 +2094,11 @@
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>64057acb86cf445aa847d5ef0d12d74c</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>91cf89d412caaf51c29ef7fe</t>
@@ -2109,7 +2121,7 @@
       <c r="AN8" s="2" t="inlineStr"/>
       <c r="AO8" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP8" s="2" t="inlineStr"/>
@@ -2151,10 +2163,22 @@
       </c>
       <c r="BG8" s="2" t="inlineStr"/>
       <c r="BH8" s="2" t="inlineStr"/>
-      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2335,182 +2359,198 @@
       <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Brown &amp; Brown</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2026-08-16T22:48:27+08:00</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>SANTOS FC Vs CSD MACARA LIVE Watchalong | Copa Sudamericana 2026 | UH Bro Sorteggio Playoff Serie C (hzm5f9zfLk)</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.118</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>主體證據不足</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9YanZhOWFhX1BLaFlpVDFpUXpBbWNBdUZXUWlhOE1TMC1TcGw0WkhzM3FnaFJFMmxxWUtDN0pHc2F3eEpSZ3A2OEhRUVlHRWJDTEpCQmh0akZQd2s?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Mshale</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>SANTOS FC 對 CSD MACARA 直播觀看 | 2026 年南美杯 |呃 Bro Sorteggio 季後賽意丙 (hzm5f9zfLk)</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>layoff</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>834743ddabec41959d1643fcc17d3ad1</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>b4b729190f5cda4073e80344</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr">
+        <is>
+          <t>6ee96ffb0e538de9b81fb7b7</t>
+        </is>
+      </c>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AK10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>0.118</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="AP10" s="2" t="inlineStr"/>
+      <c r="AQ10" s="2" t="inlineStr"/>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="inlineStr"/>
+      <c r="AT10" s="2" t="inlineStr"/>
+      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" s="2" t="inlineStr"/>
+      <c r="AX10" s="2" t="inlineStr"/>
+      <c r="AY10" s="2" t="inlineStr"/>
+      <c r="AZ10" s="2" t="inlineStr"/>
+      <c r="BA10" s="2" t="inlineStr"/>
+      <c r="BB10" s="2" t="inlineStr">
+        <is>
+          <t>BRO</t>
+        </is>
+      </c>
+      <c r="BC10" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9YanZhOWFhX1BLaFlpVDFpUXpBbWNBdUZXUWlhOE1TMC1TcGw0WkhzM3FnaFJFMmxxWUtDN0pHc2F3eEpSZ3A2OEhRUVlHRWJDTEpCQmh0akZQd2s?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>Mshale</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="inlineStr">
-        <is>
-          <t>SANTOS FC 對 CSD MACARA 直播觀看 | 2026 年南美杯 |呃 Bro Sorteggio 季後賽意丙 (hzm5f9zfLk)</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA10" s="3" t="inlineStr"/>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="3" t="inlineStr">
-        <is>
-          <t>b4b729190f5cda4073e80344</t>
-        </is>
-      </c>
-      <c r="AD10" s="3" t="inlineStr">
-        <is>
-          <t>6ee96ffb0e538de9b81fb7b7</t>
-        </is>
-      </c>
-      <c r="AE10" s="3" t="inlineStr"/>
-      <c r="AF10" s="3" t="inlineStr"/>
-      <c r="AG10" s="3" t="inlineStr"/>
-      <c r="AH10" s="3" t="inlineStr"/>
-      <c r="AI10" s="3" t="inlineStr"/>
-      <c r="AJ10" s="3" t="inlineStr"/>
-      <c r="AK10" s="3" t="inlineStr"/>
-      <c r="AL10" s="3" t="inlineStr"/>
-      <c r="AM10" s="3" t="inlineStr"/>
-      <c r="AN10" s="3" t="inlineStr"/>
-      <c r="AO10" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP10" s="3" t="inlineStr"/>
-      <c r="AQ10" s="3" t="inlineStr"/>
-      <c r="AR10" s="3" t="inlineStr"/>
-      <c r="AS10" s="3" t="inlineStr"/>
-      <c r="AT10" s="3" t="inlineStr"/>
-      <c r="AU10" s="3" t="inlineStr"/>
-      <c r="AV10" s="3" t="inlineStr"/>
-      <c r="AW10" s="3" t="inlineStr"/>
-      <c r="AX10" s="3" t="inlineStr"/>
-      <c r="AY10" s="3" t="inlineStr"/>
-      <c r="AZ10" s="3" t="inlineStr"/>
-      <c r="BA10" s="3" t="inlineStr"/>
-      <c r="BB10" s="3" t="inlineStr">
+      <c r="BD10" s="2" t="inlineStr">
         <is>
           <t>BRO</t>
         </is>
       </c>
-      <c r="BC10" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD10" s="3" t="inlineStr">
-        <is>
-          <t>BRO</t>
-        </is>
-      </c>
-      <c r="BE10" s="3" t="inlineStr">
+      <c r="BE10" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="3" t="inlineStr">
+      <c r="BF10" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="3" t="inlineStr"/>
-      <c r="BH10" s="3" t="inlineStr"/>
-      <c r="BI10" s="3" t="inlineStr"/>
-      <c r="BJ10" s="3" t="inlineStr"/>
-      <c r="BK10" s="3" t="inlineStr"/>
-      <c r="BL10" s="3" t="inlineStr"/>
+      <c r="BG10" s="2" t="inlineStr"/>
+      <c r="BH10" s="2" t="inlineStr"/>
+      <c r="BI10" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ10" s="2" t="inlineStr"/>
+      <c r="BK10" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -5465,182 +5505,206 @@
       <c r="BL26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>MCD</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>McDonald's Corporation Common Stock</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>2026-08-16T20:46:22+08:00</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Weston Vs Auburn HS Baseball Playoffs Live Mcdonald's Menu (DNpB6daVUy)</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0.012</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFAyT3hmdVh6ekN0ZTBpWHk1emRrbGpsMWZhYnlzX21yak1KTGFSaVQtMkE2V1NnUFpxN3I0Zko4MEYxcGJ1N3BTUEE1UWRNOEZGZXJ0RDlCUDkzYTA?oc=5</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Mshale</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>韋斯頓 vs 奧本高中棒球季後賽現場麥當勞菜單 (DNpB6daVUy)</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>layoff；layoffs</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>f01012134b264bcfbb7aba434d959664</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>c13b5040b8c70f603e4a60b0</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>9e7bfc6bb20e98ffd15ab1ea</t>
+        </is>
+      </c>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+      <c r="AK27" s="2" t="inlineStr"/>
+      <c r="AL27" s="2" t="inlineStr"/>
+      <c r="AM27" s="2" t="inlineStr"/>
+      <c r="AN27" s="2" t="inlineStr"/>
+      <c r="AO27" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>0.012</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="3" t="inlineStr"/>
-      <c r="R27" s="3" t="inlineStr"/>
-      <c r="S27" s="3" t="inlineStr"/>
-      <c r="T27" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFAyT3hmdVh6ekN0ZTBpWHk1emRrbGpsMWZhYnlzX21yak1KTGFSaVQtMkE2V1NnUFpxN3I0Zko4MEYxcGJ1N3BTUEE1UWRNOEZGZXJ0RDlCUDkzYTA?oc=5</t>
-        </is>
-      </c>
-      <c r="V27" s="3" t="inlineStr">
-        <is>
-          <t>Mshale</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t>韋斯頓 vs 奧本高中棒球季後賽現場麥當勞菜單 (DNpB6daVUy)</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA27" s="3" t="inlineStr"/>
-      <c r="AB27" s="3" t="inlineStr"/>
-      <c r="AC27" s="3" t="inlineStr">
-        <is>
-          <t>c13b5040b8c70f603e4a60b0</t>
-        </is>
-      </c>
-      <c r="AD27" s="3" t="inlineStr">
-        <is>
-          <t>9e7bfc6bb20e98ffd15ab1ea</t>
-        </is>
-      </c>
-      <c r="AE27" s="3" t="inlineStr"/>
-      <c r="AF27" s="3" t="inlineStr"/>
-      <c r="AG27" s="3" t="inlineStr"/>
-      <c r="AH27" s="3" t="inlineStr"/>
-      <c r="AI27" s="3" t="inlineStr"/>
-      <c r="AJ27" s="3" t="inlineStr"/>
-      <c r="AK27" s="3" t="inlineStr"/>
-      <c r="AL27" s="3" t="inlineStr"/>
-      <c r="AM27" s="3" t="inlineStr"/>
-      <c r="AN27" s="3" t="inlineStr"/>
-      <c r="AO27" s="3" t="inlineStr"/>
-      <c r="AP27" s="3" t="inlineStr"/>
-      <c r="AQ27" s="3" t="inlineStr"/>
-      <c r="AR27" s="3" t="inlineStr"/>
-      <c r="AS27" s="3" t="inlineStr"/>
-      <c r="AT27" s="3" t="inlineStr"/>
-      <c r="AU27" s="3" t="inlineStr"/>
-      <c r="AV27" s="3" t="inlineStr"/>
-      <c r="AW27" s="3" t="inlineStr">
+      <c r="AP27" s="2" t="inlineStr"/>
+      <c r="AQ27" s="2" t="inlineStr"/>
+      <c r="AR27" s="2" t="inlineStr"/>
+      <c r="AS27" s="2" t="inlineStr"/>
+      <c r="AT27" s="2" t="inlineStr"/>
+      <c r="AU27" s="2" t="inlineStr"/>
+      <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX27" s="3" t="inlineStr"/>
-      <c r="AY27" s="3" t="inlineStr"/>
-      <c r="AZ27" s="3" t="inlineStr"/>
-      <c r="BA27" s="3" t="inlineStr"/>
-      <c r="BB27" s="3" t="inlineStr">
+      <c r="AX27" s="2" t="inlineStr"/>
+      <c r="AY27" s="2" t="inlineStr"/>
+      <c r="AZ27" s="2" t="inlineStr"/>
+      <c r="BA27" s="2" t="inlineStr"/>
+      <c r="BB27" s="2" t="inlineStr">
         <is>
           <t>MCD</t>
         </is>
       </c>
-      <c r="BC27" s="3" t="inlineStr">
+      <c r="BC27" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD27" s="3" t="inlineStr"/>
-      <c r="BE27" s="3" t="inlineStr">
+      <c r="BD27" s="2" t="inlineStr"/>
+      <c r="BE27" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF27" s="3" t="inlineStr">
+      <c r="BF27" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG27" s="3" t="inlineStr">
+      <c r="BG27" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH27" s="3" t="inlineStr"/>
-      <c r="BI27" s="3" t="inlineStr"/>
-      <c r="BJ27" s="3" t="inlineStr"/>
-      <c r="BK27" s="3" t="inlineStr"/>
-      <c r="BL27" s="3" t="inlineStr"/>
+      <c r="BH27" s="2" t="inlineStr"/>
+      <c r="BI27" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ27" s="2" t="inlineStr"/>
+      <c r="BK27" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5672,32 +5736,32 @@
       <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -5741,7 +5805,7 @@
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -5750,7 +5814,11 @@
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr"/>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>02ddcba667c249f18c3b101a470e0ace</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
           <t>97b78f72c6b4bb3bd00b1f0f</t>
@@ -5773,7 +5841,7 @@
       <c r="AN28" s="2" t="inlineStr"/>
       <c r="AO28" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP28" s="2" t="inlineStr"/>
@@ -5807,10 +5875,22 @@
       <c r="BF28" s="2" t="inlineStr"/>
       <c r="BG28" s="2" t="inlineStr"/>
       <c r="BH28" s="2" t="inlineStr"/>
-      <c r="BI28" s="2" t="inlineStr"/>
+      <c r="BI28" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ28" s="2" t="inlineStr"/>
-      <c r="BK28" s="2" t="inlineStr"/>
-      <c r="BL28" s="2" t="inlineStr"/>
+      <c r="BK28" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6044,32 +6124,32 @@
       <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -6113,7 +6193,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -6122,7 +6202,11 @@
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr"/>
-      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>738ad07d693b4f58a9dced345144bba6</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>4250021e34bc480c898f53db</t>
@@ -6145,7 +6229,7 @@
       <c r="AN30" s="2" t="inlineStr"/>
       <c r="AO30" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP30" s="2" t="inlineStr"/>
@@ -6187,374 +6271,410 @@
       </c>
       <c r="BG30" s="2" t="inlineStr"/>
       <c r="BH30" s="2" t="inlineStr"/>
-      <c r="BI30" s="2" t="inlineStr"/>
+      <c r="BI30" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ30" s="2" t="inlineStr"/>
-      <c r="BK30" s="2" t="inlineStr"/>
-      <c r="BL30" s="2" t="inlineStr"/>
+      <c r="BK30" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>GM</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>General Motors</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>2026-08-16T20:33:08+08:00</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>GM John Lynch eyes big finish for 49ers in wide-open NFC playoff race</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.423</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPb1NrMWZULXowOTU5SXJhWFpGTEE4dzhiU0k3Z3hMem1ib1NGenNseGh3QXlBVDVpWDBEN1VuZTItNXR0Y2JoZVoySkFMcUlTWnhGWTBsWmFVYlM0eUdfMGNfYV9HRTFaVWVKNjF6X0ZzenVXdFhHNlVoLXRzWjFBb1U3RTJJdHFCWkE?oc=5</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Sports</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>總經理約翰林奇 (John Lynch) 希望 49 人隊在 NFC 季後賽中取得優異成績</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>layoff</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>d27a4e538bda4e2b88106e5533f14e2b</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>a2cc74f8cb4f2868b11c2b32</t>
+        </is>
+      </c>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>99167d191e8f9dfaa8138dc3</t>
+        </is>
+      </c>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+      <c r="AK31" s="2" t="inlineStr"/>
+      <c r="AL31" s="2" t="inlineStr"/>
+      <c r="AM31" s="2" t="inlineStr"/>
+      <c r="AN31" s="2" t="inlineStr"/>
+      <c r="AO31" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>0.423</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr"/>
-      <c r="Q31" s="3" t="inlineStr"/>
-      <c r="R31" s="3" t="inlineStr"/>
-      <c r="S31" s="3" t="inlineStr"/>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U31" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPb1NrMWZULXowOTU5SXJhWFpGTEE4dzhiU0k3Z3hMem1ib1NGenNseGh3QXlBVDVpWDBEN1VuZTItNXR0Y2JoZVoySkFMcUlTWnhGWTBsWmFVYlM0eUdfMGNfYV9HRTFaVWVKNjF6X0ZzenVXdFhHNlVoLXRzWjFBb1U3RTJJdHFCWkE?oc=5</t>
-        </is>
-      </c>
-      <c r="V31" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Sports</t>
-        </is>
-      </c>
-      <c r="W31" s="3" t="inlineStr">
-        <is>
-          <t>總經理約翰林奇 (John Lynch) 希望 49 人隊在 NFC 季後賽中取得優異成績</t>
-        </is>
-      </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z31" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA31" s="3" t="inlineStr"/>
-      <c r="AB31" s="3" t="inlineStr"/>
-      <c r="AC31" s="3" t="inlineStr">
-        <is>
-          <t>a2cc74f8cb4f2868b11c2b32</t>
-        </is>
-      </c>
-      <c r="AD31" s="3" t="inlineStr">
-        <is>
-          <t>99167d191e8f9dfaa8138dc3</t>
-        </is>
-      </c>
-      <c r="AE31" s="3" t="inlineStr"/>
-      <c r="AF31" s="3" t="inlineStr"/>
-      <c r="AG31" s="3" t="inlineStr"/>
-      <c r="AH31" s="3" t="inlineStr"/>
-      <c r="AI31" s="3" t="inlineStr"/>
-      <c r="AJ31" s="3" t="inlineStr"/>
-      <c r="AK31" s="3" t="inlineStr"/>
-      <c r="AL31" s="3" t="inlineStr"/>
-      <c r="AM31" s="3" t="inlineStr"/>
-      <c r="AN31" s="3" t="inlineStr"/>
-      <c r="AO31" s="3" t="inlineStr"/>
-      <c r="AP31" s="3" t="inlineStr"/>
-      <c r="AQ31" s="3" t="inlineStr"/>
-      <c r="AR31" s="3" t="inlineStr"/>
-      <c r="AS31" s="3" t="inlineStr"/>
-      <c r="AT31" s="3" t="inlineStr"/>
-      <c r="AU31" s="3" t="inlineStr"/>
-      <c r="AV31" s="3" t="inlineStr"/>
-      <c r="AW31" s="3" t="inlineStr"/>
-      <c r="AX31" s="3" t="inlineStr"/>
-      <c r="AY31" s="3" t="inlineStr"/>
-      <c r="AZ31" s="3" t="inlineStr"/>
-      <c r="BA31" s="3" t="inlineStr"/>
-      <c r="BB31" s="3" t="inlineStr">
+      <c r="AP31" s="2" t="inlineStr"/>
+      <c r="AQ31" s="2" t="inlineStr"/>
+      <c r="AR31" s="2" t="inlineStr"/>
+      <c r="AS31" s="2" t="inlineStr"/>
+      <c r="AT31" s="2" t="inlineStr"/>
+      <c r="AU31" s="2" t="inlineStr"/>
+      <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" s="2" t="inlineStr"/>
+      <c r="AX31" s="2" t="inlineStr"/>
+      <c r="AY31" s="2" t="inlineStr"/>
+      <c r="AZ31" s="2" t="inlineStr"/>
+      <c r="BA31" s="2" t="inlineStr"/>
+      <c r="BB31" s="2" t="inlineStr">
         <is>
           <t>GM</t>
         </is>
       </c>
-      <c r="BC31" s="3" t="inlineStr">
+      <c r="BC31" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD31" s="3" t="inlineStr"/>
-      <c r="BE31" s="3" t="inlineStr">
+      <c r="BD31" s="2" t="inlineStr"/>
+      <c r="BE31" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF31" s="3" t="inlineStr"/>
-      <c r="BG31" s="3" t="inlineStr">
+      <c r="BF31" s="2" t="inlineStr"/>
+      <c r="BG31" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH31" s="3" t="inlineStr"/>
-      <c r="BI31" s="3" t="inlineStr"/>
-      <c r="BJ31" s="3" t="inlineStr"/>
-      <c r="BK31" s="3" t="inlineStr"/>
-      <c r="BL31" s="3" t="inlineStr"/>
+      <c r="BH31" s="2" t="inlineStr"/>
+      <c r="BI31" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ31" s="2" t="inlineStr"/>
+      <c r="BK31" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>FSLR</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>First Solar, Inc.</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>2026-08-16T19:38:27+08:00</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>FSLR Stockholders Have Opportunity to Lead First Solar, Inc. Class Action Lawsuit – Contact Bronstein, Gewirtz and Grossman, LLC Today!</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>重大訴訟</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="L32" s="4" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>人工覆核</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
+      <c r="N32" s="3" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O32" s="4" t="inlineStr">
+      <c r="O32" s="3" t="inlineStr">
         <is>
           <t>0.053</t>
         </is>
       </c>
-      <c r="P32" s="4" t="inlineStr"/>
-      <c r="Q32" s="4" t="inlineStr"/>
-      <c r="R32" s="4" t="inlineStr"/>
-      <c r="S32" s="4" t="inlineStr"/>
-      <c r="T32" s="4" t="inlineStr">
+      <c r="P32" s="3" t="inlineStr"/>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr"/>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U32" s="4" t="inlineStr">
+      <c r="U32" s="3" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPYTRpVkpjZkxxY0JlcS1TeUVvaGRDRzUtMzFDMFFGRUZkYjNQMWFLOUVjdjFlNUdsMUNsRE5ZSWhUTHJYcEdNQmxuUFM4TC1PNENMTUQ1WVJDTk9YcmlGY0szRThtdHM3ZXFUVy1BcGhfQnB1RW1zNWtDTHk4ek94MzZ3bzBFbkdZZHFZZzNjMXI4b2FsQXpEUkktMF9iTUVwSWVSMEducmExRGVRS2VvdjBnQllOSmJOcHRkYl8yNlF1c0RCY3E2ckZkWHFBUmtERVgwSHUxT2pIS1VWb1FFZnREa2I?oc=5</t>
         </is>
       </c>
-      <c r="V32" s="4" t="inlineStr">
+      <c r="V32" s="3" t="inlineStr">
         <is>
           <t>ACCESS Newswire</t>
         </is>
       </c>
-      <c r="W32" s="4" t="inlineStr">
+      <c r="W32" s="3" t="inlineStr">
         <is>
           <t>FSLR 股東有機會領導 First Solar, Inc. 集體訴訟 – 立即聯繫 Bronstein、Gewirtz 和 Grossman, LLC！</t>
         </is>
       </c>
-      <c r="X32" s="4" t="inlineStr">
+      <c r="X32" s="3" t="inlineStr">
         <is>
           <t>LEGAL</t>
         </is>
       </c>
-      <c r="Y32" s="4" t="inlineStr">
+      <c r="Y32" s="3" t="inlineStr">
         <is>
           <t>MAJOR_LITIGATION</t>
         </is>
       </c>
-      <c r="Z32" s="4" t="inlineStr">
+      <c r="Z32" s="3" t="inlineStr">
         <is>
           <t>class action</t>
         </is>
       </c>
-      <c r="AA32" s="4" t="inlineStr"/>
-      <c r="AB32" s="4" t="inlineStr">
+      <c r="AA32" s="3" t="inlineStr"/>
+      <c r="AB32" s="3" t="inlineStr">
         <is>
           <t>fe7f351f050843908b8b3fac725cc668</t>
         </is>
       </c>
-      <c r="AC32" s="4" t="inlineStr">
+      <c r="AC32" s="3" t="inlineStr">
         <is>
           <t>b1915ec4a2488bc955728b02</t>
         </is>
       </c>
-      <c r="AD32" s="4" t="inlineStr">
+      <c r="AD32" s="3" t="inlineStr">
         <is>
           <t>d4cfd68254a8e4063b3c0497</t>
         </is>
       </c>
-      <c r="AE32" s="4" t="inlineStr"/>
-      <c r="AF32" s="4" t="inlineStr"/>
-      <c r="AG32" s="4" t="inlineStr"/>
-      <c r="AH32" s="4" t="inlineStr"/>
-      <c r="AI32" s="4" t="inlineStr"/>
-      <c r="AJ32" s="4" t="inlineStr"/>
-      <c r="AK32" s="4" t="inlineStr"/>
-      <c r="AL32" s="4" t="inlineStr"/>
-      <c r="AM32" s="4" t="inlineStr"/>
-      <c r="AN32" s="4" t="inlineStr"/>
-      <c r="AO32" s="4" t="inlineStr">
+      <c r="AE32" s="3" t="inlineStr"/>
+      <c r="AF32" s="3" t="inlineStr"/>
+      <c r="AG32" s="3" t="inlineStr"/>
+      <c r="AH32" s="3" t="inlineStr"/>
+      <c r="AI32" s="3" t="inlineStr"/>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr"/>
+      <c r="AM32" s="3" t="inlineStr"/>
+      <c r="AN32" s="3" t="inlineStr"/>
+      <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AP32" s="4" t="inlineStr"/>
-      <c r="AQ32" s="4" t="inlineStr"/>
-      <c r="AR32" s="4" t="inlineStr"/>
-      <c r="AS32" s="4" t="inlineStr"/>
-      <c r="AT32" s="4" t="inlineStr"/>
-      <c r="AU32" s="4" t="inlineStr"/>
-      <c r="AV32" s="4" t="inlineStr"/>
-      <c r="AW32" s="4" t="inlineStr">
+      <c r="AP32" s="3" t="inlineStr"/>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr"/>
+      <c r="AS32" s="3" t="inlineStr"/>
+      <c r="AT32" s="3" t="inlineStr"/>
+      <c r="AU32" s="3" t="inlineStr"/>
+      <c r="AV32" s="3" t="inlineStr"/>
+      <c r="AW32" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX32" s="4" t="inlineStr"/>
-      <c r="AY32" s="4" t="inlineStr"/>
-      <c r="AZ32" s="4" t="inlineStr"/>
-      <c r="BA32" s="4" t="inlineStr"/>
-      <c r="BB32" s="4" t="inlineStr">
+      <c r="AX32" s="3" t="inlineStr"/>
+      <c r="AY32" s="3" t="inlineStr"/>
+      <c r="AZ32" s="3" t="inlineStr"/>
+      <c r="BA32" s="3" t="inlineStr"/>
+      <c r="BB32" s="3" t="inlineStr">
         <is>
           <t>FSLR</t>
         </is>
       </c>
-      <c r="BC32" s="4" t="inlineStr">
+      <c r="BC32" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD32" s="4" t="inlineStr"/>
-      <c r="BE32" s="4" t="inlineStr">
+      <c r="BD32" s="3" t="inlineStr"/>
+      <c r="BE32" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF32" s="4" t="inlineStr">
+      <c r="BF32" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG32" s="4" t="inlineStr">
+      <c r="BG32" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH32" s="4" t="inlineStr"/>
-      <c r="BI32" s="4" t="inlineStr"/>
-      <c r="BJ32" s="4" t="inlineStr"/>
-      <c r="BK32" s="4" t="inlineStr">
+      <c r="BH32" s="3" t="inlineStr"/>
+      <c r="BI32" s="3" t="inlineStr"/>
+      <c r="BJ32" s="3" t="inlineStr"/>
+      <c r="BK32" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL32" s="4" t="inlineStr">
+      <c r="BL32" s="3" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
@@ -7116,32 +7236,32 @@
       <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -7185,7 +7305,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -7194,7 +7314,11 @@
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr"/>
-      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>d1b26af900034778971c6584d9a092f6</t>
+        </is>
+      </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
           <t>875f1b9415924987a9bf94b9</t>
@@ -7217,7 +7341,7 @@
       <c r="AN36" s="2" t="inlineStr"/>
       <c r="AO36" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP36" s="2" t="inlineStr"/>
@@ -7259,10 +7383,22 @@
       </c>
       <c r="BG36" s="2" t="inlineStr"/>
       <c r="BH36" s="2" t="inlineStr"/>
-      <c r="BI36" s="2" t="inlineStr"/>
+      <c r="BI36" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ36" s="2" t="inlineStr"/>
-      <c r="BK36" s="2" t="inlineStr"/>
-      <c r="BL36" s="2" t="inlineStr"/>
+      <c r="BK36" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7645,182 +7781,206 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>DOW</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Dow Inc. Common Stock </t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>2026-08-16T17:40:29+08:00</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Bloomberg Money Minute: Dow Hits Record High As SpaceX Plunges Canada Revenue Agency Data Breaches (Kz5b0Hg4QP)</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0.197</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBTNzRpUEoxUGR0MkdUWkFld0xOblN1SEh1U3VnQWU2dDkyaXVta1NzTUhiRU8ycXlpeXZNUTZCd1N3VmhHLTdPQ1RsdUJvUWNnc2ZfTnpCbEY5a0U?oc=5</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Mshale</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>彭博財經紀要：隨著 SpaceX 暴跌，道瓊指數創下歷史新高 加拿大稅務局資料外洩 (Kz5b0Hg4QP)</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>CYBER</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>data breach</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>09239d28b3e741b19960c557e6cb99af</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>f2b86040989baf9e42cfee63</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>7031ef56aea01413bbc14779</t>
+        </is>
+      </c>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
+      <c r="AJ39" s="2" t="inlineStr"/>
+      <c r="AK39" s="2" t="inlineStr"/>
+      <c r="AL39" s="2" t="inlineStr"/>
+      <c r="AM39" s="2" t="inlineStr"/>
+      <c r="AN39" s="2" t="inlineStr"/>
+      <c r="AO39" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>0.197</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr"/>
-      <c r="Q39" s="3" t="inlineStr"/>
-      <c r="R39" s="3" t="inlineStr"/>
-      <c r="S39" s="3" t="inlineStr"/>
-      <c r="T39" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBTNzRpUEoxUGR0MkdUWkFld0xOblN1SEh1U3VnQWU2dDkyaXVta1NzTUhiRU8ycXlpeXZNUTZCd1N3VmhHLTdPQ1RsdUJvUWNnc2ZfTnpCbEY5a0U?oc=5</t>
-        </is>
-      </c>
-      <c r="V39" s="3" t="inlineStr">
-        <is>
-          <t>Mshale</t>
-        </is>
-      </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t>彭博財經紀要：隨著 SpaceX 暴跌，道瓊指數創下歷史新高 加拿大稅務局資料外洩 (Kz5b0Hg4QP)</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y39" s="3" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z39" s="3" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA39" s="3" t="inlineStr"/>
-      <c r="AB39" s="3" t="inlineStr"/>
-      <c r="AC39" s="3" t="inlineStr">
-        <is>
-          <t>f2b86040989baf9e42cfee63</t>
-        </is>
-      </c>
-      <c r="AD39" s="3" t="inlineStr">
-        <is>
-          <t>7031ef56aea01413bbc14779</t>
-        </is>
-      </c>
-      <c r="AE39" s="3" t="inlineStr"/>
-      <c r="AF39" s="3" t="inlineStr"/>
-      <c r="AG39" s="3" t="inlineStr"/>
-      <c r="AH39" s="3" t="inlineStr"/>
-      <c r="AI39" s="3" t="inlineStr"/>
-      <c r="AJ39" s="3" t="inlineStr"/>
-      <c r="AK39" s="3" t="inlineStr"/>
-      <c r="AL39" s="3" t="inlineStr"/>
-      <c r="AM39" s="3" t="inlineStr"/>
-      <c r="AN39" s="3" t="inlineStr"/>
-      <c r="AO39" s="3" t="inlineStr"/>
-      <c r="AP39" s="3" t="inlineStr"/>
-      <c r="AQ39" s="3" t="inlineStr"/>
-      <c r="AR39" s="3" t="inlineStr"/>
-      <c r="AS39" s="3" t="inlineStr"/>
-      <c r="AT39" s="3" t="inlineStr"/>
-      <c r="AU39" s="3" t="inlineStr"/>
-      <c r="AV39" s="3" t="inlineStr"/>
-      <c r="AW39" s="3" t="inlineStr">
+      <c r="AP39" s="2" t="inlineStr"/>
+      <c r="AQ39" s="2" t="inlineStr"/>
+      <c r="AR39" s="2" t="inlineStr"/>
+      <c r="AS39" s="2" t="inlineStr"/>
+      <c r="AT39" s="2" t="inlineStr"/>
+      <c r="AU39" s="2" t="inlineStr"/>
+      <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX39" s="3" t="inlineStr"/>
-      <c r="AY39" s="3" t="inlineStr"/>
-      <c r="AZ39" s="3" t="inlineStr"/>
-      <c r="BA39" s="3" t="inlineStr"/>
-      <c r="BB39" s="3" t="inlineStr">
+      <c r="AX39" s="2" t="inlineStr"/>
+      <c r="AY39" s="2" t="inlineStr"/>
+      <c r="AZ39" s="2" t="inlineStr"/>
+      <c r="BA39" s="2" t="inlineStr"/>
+      <c r="BB39" s="2" t="inlineStr">
         <is>
           <t>DOW</t>
         </is>
       </c>
-      <c r="BC39" s="3" t="inlineStr">
+      <c r="BC39" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD39" s="3" t="inlineStr"/>
-      <c r="BE39" s="3" t="inlineStr">
+      <c r="BD39" s="2" t="inlineStr"/>
+      <c r="BE39" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF39" s="3" t="inlineStr">
+      <c r="BF39" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG39" s="3" t="inlineStr">
+      <c r="BG39" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH39" s="3" t="inlineStr"/>
-      <c r="BI39" s="3" t="inlineStr"/>
-      <c r="BJ39" s="3" t="inlineStr"/>
-      <c r="BK39" s="3" t="inlineStr"/>
-      <c r="BL39" s="3" t="inlineStr"/>
+      <c r="BH39" s="2" t="inlineStr"/>
+      <c r="BI39" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ39" s="2" t="inlineStr"/>
+      <c r="BK39" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -8208,32 +8368,32 @@
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -8277,7 +8437,7 @@
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -8286,7 +8446,11 @@
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr"/>
-      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>c97ed5448d69435581bc17434ae8669f</t>
+        </is>
+      </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
           <t>ba3d714f5b7b6e88b252e3bc</t>
@@ -8309,7 +8473,7 @@
       <c r="AN42" s="2" t="inlineStr"/>
       <c r="AO42" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP42" s="2" t="inlineStr"/>
@@ -8351,180 +8515,216 @@
       </c>
       <c r="BG42" s="2" t="inlineStr"/>
       <c r="BH42" s="2" t="inlineStr"/>
-      <c r="BI42" s="2" t="inlineStr"/>
+      <c r="BI42" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ42" s="2" t="inlineStr"/>
-      <c r="BK42" s="2" t="inlineStr"/>
-      <c r="BL42" s="2" t="inlineStr"/>
+      <c r="BK42" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>COIN</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Coinbase</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>2026-08-16T16:03:58+08:00</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Bitcoin demand weakens as Coinbase premium inde...</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>'-0.947</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQczhZLW84MjR0NmNrcVE5LVRvLW1LTm5xMDJxaUl6cXBfbERFV3R1N1ROa0p4RWExbkZuOVJQT19nWV93RWdJamtqNVY2bURoeUFUczdBY2J3eUJEVkhBTkE3dXNaUG9WYzdtVmdJSUhtSDlyRXR6b2JETU9zTVAzdDkyMmNFNTNTSGc?oc=5</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Pluang</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>隨著 Coinbase 溢價指數下降，比特幣需求減弱</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>demand weakens</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>2ed0314b48194574b2481336160eb0d5</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>dedd5344f34e3e3828bebfeb</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>8223eec336e2ca59113293fd</t>
+        </is>
+      </c>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AI43" s="2" t="inlineStr"/>
+      <c r="AJ43" s="2" t="inlineStr"/>
+      <c r="AK43" s="2" t="inlineStr"/>
+      <c r="AL43" s="2" t="inlineStr"/>
+      <c r="AM43" s="2" t="inlineStr"/>
+      <c r="AN43" s="2" t="inlineStr"/>
+      <c r="AO43" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>'-0.947</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
-      <c r="R43" s="3" t="inlineStr"/>
-      <c r="S43" s="3" t="inlineStr"/>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQczhZLW84MjR0NmNrcVE5LVRvLW1LTm5xMDJxaUl6cXBfbERFV3R1N1ROa0p4RWExbkZuOVJQT19nWV93RWdJamtqNVY2bURoeUFUczdBY2J3eUJEVkhBTkE3dXNaUG9WYzdtVmdJSUhtSDlyRXR6b2JETU9zTVAzdDkyMmNFNTNTSGc?oc=5</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t>Pluang</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t>隨著 Coinbase 溢價指數下降，比特幣需求減弱</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="inlineStr">
-        <is>
-          <t>demand weakens</t>
-        </is>
-      </c>
-      <c r="AA43" s="3" t="inlineStr"/>
-      <c r="AB43" s="3" t="inlineStr"/>
-      <c r="AC43" s="3" t="inlineStr">
-        <is>
-          <t>dedd5344f34e3e3828bebfeb</t>
-        </is>
-      </c>
-      <c r="AD43" s="3" t="inlineStr">
-        <is>
-          <t>8223eec336e2ca59113293fd</t>
-        </is>
-      </c>
-      <c r="AE43" s="3" t="inlineStr"/>
-      <c r="AF43" s="3" t="inlineStr"/>
-      <c r="AG43" s="3" t="inlineStr"/>
-      <c r="AH43" s="3" t="inlineStr"/>
-      <c r="AI43" s="3" t="inlineStr"/>
-      <c r="AJ43" s="3" t="inlineStr"/>
-      <c r="AK43" s="3" t="inlineStr"/>
-      <c r="AL43" s="3" t="inlineStr"/>
-      <c r="AM43" s="3" t="inlineStr"/>
-      <c r="AN43" s="3" t="inlineStr"/>
-      <c r="AO43" s="3" t="inlineStr"/>
-      <c r="AP43" s="3" t="inlineStr"/>
-      <c r="AQ43" s="3" t="inlineStr"/>
-      <c r="AR43" s="3" t="inlineStr"/>
-      <c r="AS43" s="3" t="inlineStr"/>
-      <c r="AT43" s="3" t="inlineStr"/>
-      <c r="AU43" s="3" t="inlineStr"/>
-      <c r="AV43" s="3" t="inlineStr"/>
-      <c r="AW43" s="3" t="inlineStr"/>
-      <c r="AX43" s="3" t="inlineStr"/>
-      <c r="AY43" s="3" t="inlineStr"/>
-      <c r="AZ43" s="3" t="inlineStr"/>
-      <c r="BA43" s="3" t="inlineStr"/>
-      <c r="BB43" s="3" t="inlineStr">
+      <c r="AP43" s="2" t="inlineStr"/>
+      <c r="AQ43" s="2" t="inlineStr"/>
+      <c r="AR43" s="2" t="inlineStr"/>
+      <c r="AS43" s="2" t="inlineStr"/>
+      <c r="AT43" s="2" t="inlineStr"/>
+      <c r="AU43" s="2" t="inlineStr"/>
+      <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" s="2" t="inlineStr"/>
+      <c r="AX43" s="2" t="inlineStr"/>
+      <c r="AY43" s="2" t="inlineStr"/>
+      <c r="AZ43" s="2" t="inlineStr"/>
+      <c r="BA43" s="2" t="inlineStr"/>
+      <c r="BB43" s="2" t="inlineStr">
         <is>
           <t>COIN</t>
         </is>
       </c>
-      <c r="BC43" s="3" t="inlineStr">
+      <c r="BC43" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD43" s="3" t="inlineStr"/>
-      <c r="BE43" s="3" t="inlineStr">
+      <c r="BD43" s="2" t="inlineStr"/>
+      <c r="BE43" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF43" s="3" t="inlineStr"/>
-      <c r="BG43" s="3" t="inlineStr">
+      <c r="BF43" s="2" t="inlineStr"/>
+      <c r="BG43" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH43" s="3" t="inlineStr"/>
-      <c r="BI43" s="3" t="inlineStr"/>
-      <c r="BJ43" s="3" t="inlineStr"/>
-      <c r="BK43" s="3" t="inlineStr"/>
-      <c r="BL43" s="3" t="inlineStr"/>
+      <c r="BH43" s="2" t="inlineStr"/>
+      <c r="BI43" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ43" s="2" t="inlineStr"/>
+      <c r="BK43" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8721,174 +8921,198 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Boeing</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>2026-08-16T15:24:44+08:00</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Stewart Cink beats Miguel Angel Jiménez in playoff to win Boeing Classic, earns fifth title of season</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K45" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0.243</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOaUFhMGUxRXNPeDVmVjV2ajd5Y0VEMHQ3X3E1QVdkLWZYMnpOSjdqX281SjdCYmhkdXpRc1hSRXVoSkdweWs5OXVNa1NENHNpdWVWS25falJkM2FfcC1fUGR3alJKQ0R0QlU4eTFwZ0RVcVFFV1RqWkl5ZWNoV1dYZG1OeGRuZ05JUE11Q2ZjeHVhck8wRzFROFRHdGZIM0VKQ1Ytc2N0a0w0S0QzZlVEMWlnckVTRXFSQmNxZk8xU01NbDBnTE5OUUlIaU9KNFdBT3dPWW5Kb0lxdnZhX1RtR1REeWk2VG5qSDlyUDdrRFVtWHM?oc=5</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>PGA Tour</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>史都華辛克在延長賽中擊敗米格爾安赫爾希門尼斯贏得波音精英賽冠軍，贏得本賽季第五個冠軍</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>layoff</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0d79549b611c4e1eaef6a32e4d1432a3</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>b17bd1aca568811c85b8e436</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>f2ba7dc9e87612963ae7af5e</t>
+        </is>
+      </c>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
+      <c r="AJ45" s="2" t="inlineStr"/>
+      <c r="AK45" s="2" t="inlineStr"/>
+      <c r="AL45" s="2" t="inlineStr"/>
+      <c r="AM45" s="2" t="inlineStr"/>
+      <c r="AN45" s="2" t="inlineStr"/>
+      <c r="AO45" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N45" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>0.243</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr"/>
-      <c r="Q45" s="3" t="inlineStr"/>
-      <c r="R45" s="3" t="inlineStr"/>
-      <c r="S45" s="3" t="inlineStr"/>
-      <c r="T45" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U45" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOaUFhMGUxRXNPeDVmVjV2ajd5Y0VEMHQ3X3E1QVdkLWZYMnpOSjdqX281SjdCYmhkdXpRc1hSRXVoSkdweWs5OXVNa1NENHNpdWVWS25falJkM2FfcC1fUGR3alJKQ0R0QlU4eTFwZ0RVcVFFV1RqWkl5ZWNoV1dYZG1OeGRuZ05JUE11Q2ZjeHVhck8wRzFROFRHdGZIM0VKQ1Ytc2N0a0w0S0QzZlVEMWlnckVTRXFSQmNxZk8xU01NbDBnTE5OUUlIaU9KNFdBT3dPWW5Kb0lxdnZhX1RtR1REeWk2VG5qSDlyUDdrRFVtWHM?oc=5</t>
-        </is>
-      </c>
-      <c r="V45" s="3" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t>史都華辛克在延長賽中擊敗米格爾安赫爾希門尼斯贏得波音精英賽冠軍，贏得本賽季第五個冠軍</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y45" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA45" s="3" t="inlineStr"/>
-      <c r="AB45" s="3" t="inlineStr"/>
-      <c r="AC45" s="3" t="inlineStr">
-        <is>
-          <t>b17bd1aca568811c85b8e436</t>
-        </is>
-      </c>
-      <c r="AD45" s="3" t="inlineStr">
-        <is>
-          <t>f2ba7dc9e87612963ae7af5e</t>
-        </is>
-      </c>
-      <c r="AE45" s="3" t="inlineStr"/>
-      <c r="AF45" s="3" t="inlineStr"/>
-      <c r="AG45" s="3" t="inlineStr"/>
-      <c r="AH45" s="3" t="inlineStr"/>
-      <c r="AI45" s="3" t="inlineStr"/>
-      <c r="AJ45" s="3" t="inlineStr"/>
-      <c r="AK45" s="3" t="inlineStr"/>
-      <c r="AL45" s="3" t="inlineStr"/>
-      <c r="AM45" s="3" t="inlineStr"/>
-      <c r="AN45" s="3" t="inlineStr"/>
-      <c r="AO45" s="3" t="inlineStr"/>
-      <c r="AP45" s="3" t="inlineStr"/>
-      <c r="AQ45" s="3" t="inlineStr"/>
-      <c r="AR45" s="3" t="inlineStr"/>
-      <c r="AS45" s="3" t="inlineStr"/>
-      <c r="AT45" s="3" t="inlineStr"/>
-      <c r="AU45" s="3" t="inlineStr"/>
-      <c r="AV45" s="3" t="inlineStr"/>
-      <c r="AW45" s="3" t="inlineStr"/>
-      <c r="AX45" s="3" t="inlineStr"/>
-      <c r="AY45" s="3" t="inlineStr"/>
-      <c r="AZ45" s="3" t="inlineStr"/>
-      <c r="BA45" s="3" t="inlineStr"/>
-      <c r="BB45" s="3" t="inlineStr">
+      <c r="AP45" s="2" t="inlineStr"/>
+      <c r="AQ45" s="2" t="inlineStr"/>
+      <c r="AR45" s="2" t="inlineStr"/>
+      <c r="AS45" s="2" t="inlineStr"/>
+      <c r="AT45" s="2" t="inlineStr"/>
+      <c r="AU45" s="2" t="inlineStr"/>
+      <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" s="2" t="inlineStr"/>
+      <c r="AX45" s="2" t="inlineStr"/>
+      <c r="AY45" s="2" t="inlineStr"/>
+      <c r="AZ45" s="2" t="inlineStr"/>
+      <c r="BA45" s="2" t="inlineStr"/>
+      <c r="BB45" s="2" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="BC45" s="3" t="inlineStr">
+      <c r="BC45" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD45" s="3" t="inlineStr"/>
-      <c r="BE45" s="3" t="inlineStr">
+      <c r="BD45" s="2" t="inlineStr"/>
+      <c r="BE45" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF45" s="3" t="inlineStr"/>
-      <c r="BG45" s="3" t="inlineStr">
+      <c r="BF45" s="2" t="inlineStr"/>
+      <c r="BG45" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH45" s="3" t="inlineStr"/>
-      <c r="BI45" s="3" t="inlineStr"/>
-      <c r="BJ45" s="3" t="inlineStr"/>
-      <c r="BK45" s="3" t="inlineStr"/>
-      <c r="BL45" s="3" t="inlineStr"/>
+      <c r="BH45" s="2" t="inlineStr"/>
+      <c r="BI45" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ45" s="2" t="inlineStr"/>
+      <c r="BK45" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -9292,32 +9516,32 @@
       <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -9361,7 +9585,7 @@
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -9370,7 +9594,11 @@
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr"/>
-      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>4874850afc15438ebcc43a78800db28a</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
           <t>682286533d48fb779fb80365</t>
@@ -9393,7 +9621,7 @@
       <c r="AN48" s="2" t="inlineStr"/>
       <c r="AO48" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP48" s="2" t="inlineStr"/>
@@ -9427,10 +9655,22 @@
       <c r="BF48" s="2" t="inlineStr"/>
       <c r="BG48" s="2" t="inlineStr"/>
       <c r="BH48" s="2" t="inlineStr"/>
-      <c r="BI48" s="2" t="inlineStr"/>
+      <c r="BI48" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ48" s="2" t="inlineStr"/>
-      <c r="BK48" s="2" t="inlineStr"/>
-      <c r="BL48" s="2" t="inlineStr"/>
+      <c r="BK48" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -10004,32 +10244,32 @@
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -10073,7 +10313,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -10082,7 +10322,11 @@
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr"/>
-      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>e496fde6b1af47f9a2905e924e41a53c</t>
+        </is>
+      </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
           <t>1986a3c39c42d432ef952936</t>
@@ -10105,7 +10349,7 @@
       <c r="AN52" s="2" t="inlineStr"/>
       <c r="AO52" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP52" s="2" t="inlineStr"/>
@@ -10147,10 +10391,22 @@
       </c>
       <c r="BG52" s="2" t="inlineStr"/>
       <c r="BH52" s="2" t="inlineStr"/>
-      <c r="BI52" s="2" t="inlineStr"/>
+      <c r="BI52" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ52" s="2" t="inlineStr"/>
-      <c r="BK52" s="2" t="inlineStr"/>
-      <c r="BL52" s="2" t="inlineStr"/>
+      <c r="BK52" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10182,32 +10438,32 @@
       <c r="G53" s="2" t="inlineStr"/>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -10251,7 +10507,7 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -10260,7 +10516,11 @@
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr"/>
-      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0f64f10bc22b402380207f8b3c52be9b</t>
+        </is>
+      </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
           <t>2b786e797103f1c9cea4665b</t>
@@ -10283,7 +10543,7 @@
       <c r="AN53" s="2" t="inlineStr"/>
       <c r="AO53" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP53" s="2" t="inlineStr"/>
@@ -10317,10 +10577,22 @@
       <c r="BF53" s="2" t="inlineStr"/>
       <c r="BG53" s="2" t="inlineStr"/>
       <c r="BH53" s="2" t="inlineStr"/>
-      <c r="BI53" s="2" t="inlineStr"/>
+      <c r="BI53" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ53" s="2" t="inlineStr"/>
-      <c r="BK53" s="2" t="inlineStr"/>
-      <c r="BL53" s="2" t="inlineStr"/>
+      <c r="BK53" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL53" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10352,32 +10624,32 @@
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -10421,7 +10693,7 @@
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -10430,7 +10702,11 @@
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr"/>
-      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>8d640713668d41fdb289c28e91e87e0b</t>
+        </is>
+      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
           <t>2b786e797103f1c9cea4665b</t>
@@ -10453,7 +10729,7 @@
       <c r="AN54" s="2" t="inlineStr"/>
       <c r="AO54" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP54" s="2" t="inlineStr"/>
@@ -10487,10 +10763,22 @@
       <c r="BF54" s="2" t="inlineStr"/>
       <c r="BG54" s="2" t="inlineStr"/>
       <c r="BH54" s="2" t="inlineStr"/>
-      <c r="BI54" s="2" t="inlineStr"/>
+      <c r="BI54" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ54" s="2" t="inlineStr"/>
-      <c r="BK54" s="2" t="inlineStr"/>
-      <c r="BL54" s="2" t="inlineStr"/>
+      <c r="BK54" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -11734,7 +12022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL8"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12136,51 +12424,55 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>FSLR</t>
+        </is>
+      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>First Solar, Inc.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16T22:48:27+08:00</t>
+          <t>2026-08-16T19:38:27+08:00</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>SANTOS FC Vs CSD MACARA LIVE Watchalong | Copa Sudamericana 2026 | UH Bro Sorteggio Playoff Serie C (hzm5f9zfLk)</t>
+          <t>FSLR Stockholders Have Opportunity to Lead First Solar, Inc. Class Action Lawsuit – Contact Bronstein, Gewirtz and Grossman, LLC Today!</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>裁員或人力縮減</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -12190,7 +12482,7 @@
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>0.053</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr"/>
@@ -12199,49 +12491,53 @@
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
+          <t>公司清單／別名核對</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9YanZhOWFhX1BLaFlpVDFpUXpBbWNBdUZXUWlhOE1TMC1TcGw0WkhzM3FnaFJFMmxxWUtDN0pHc2F3eEpSZ3A2OEhRUVlHRWJDTEpCQmh0akZQd2s?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPYTRpVkpjZkxxY0JlcS1TeUVvaGRDRzUtMzFDMFFGRUZkYjNQMWFLOUVjdjFlNUdsMUNsRE5ZSWhUTHJYcEdNQmxuUFM4TC1PNENMTUQ1WVJDTk9YcmlGY0szRThtdHM3ZXFUVy1BcGhfQnB1RW1zNWtDTHk4ek94MzZ3bzBFbkdZZHFZZzNjMXI4b2FsQXpEUkktMF9iTUVwSWVSMEducmExRGVRS2VvdjBnQllOSmJOcHRkYl8yNlF1c0RCY3E2ckZkWHFBUmtERVgwSHUxT2pIS1VWb1FFZnREa2I?oc=5</t>
         </is>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
-          <t>Mshale</t>
+          <t>ACCESS Newswire</t>
         </is>
       </c>
       <c r="W2" s="3" t="inlineStr">
         <is>
-          <t>SANTOS FC 對 CSD MACARA 直播觀看 | 2026 年南美杯 |呃 Bro Sorteggio 季後賽意丙 (hzm5f9zfLk)</t>
+          <t>FSLR 股東有機會領導 First Solar, Inc. 集體訴訟 – 立即聯繫 Bronstein、Gewirtz 和 Grossman, LLC！</t>
         </is>
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>OPERATIONS</t>
+          <t>LEGAL</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>WORKFORCE_REDUCTION</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
-          <t>layoff</t>
+          <t>class action</t>
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>fe7f351f050843908b8b3fac725cc668</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
-          <t>b4b729190f5cda4073e80344</t>
+          <t>b1915ec4a2488bc955728b02</t>
         </is>
       </c>
       <c r="AD2" s="3" t="inlineStr">
         <is>
-          <t>6ee96ffb0e538de9b81fb7b7</t>
+          <t>d4cfd68254a8e4063b3c0497</t>
         </is>
       </c>
       <c r="AE2" s="3" t="inlineStr"/>
@@ -12256,7 +12552,7 @@
       <c r="AN2" s="3" t="inlineStr"/>
       <c r="AO2" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" s="3" t="inlineStr"/>
@@ -12266,1109 +12562,57 @@
       <c r="AT2" s="3" t="inlineStr"/>
       <c r="AU2" s="3" t="inlineStr"/>
       <c r="AV2" s="3" t="inlineStr"/>
-      <c r="AW2" s="3" t="inlineStr"/>
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
       <c r="AX2" s="3" t="inlineStr"/>
       <c r="AY2" s="3" t="inlineStr"/>
       <c r="AZ2" s="3" t="inlineStr"/>
       <c r="BA2" s="3" t="inlineStr"/>
       <c r="BB2" s="3" t="inlineStr">
         <is>
-          <t>BRO</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="BC2" s="3" t="inlineStr">
         <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="3" t="inlineStr">
-        <is>
-          <t>BRO</t>
-        </is>
-      </c>
+          <t>已核對</t>
+        </is>
+      </c>
+      <c r="BD2" s="3" t="inlineStr"/>
       <c r="BE2" s="3" t="inlineStr">
         <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
       <c r="BF2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="3" t="inlineStr"/>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG2" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
       <c r="BH2" s="3" t="inlineStr"/>
       <c r="BI2" s="3" t="inlineStr"/>
       <c r="BJ2" s="3" t="inlineStr"/>
-      <c r="BK2" s="3" t="inlineStr"/>
-      <c r="BL2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>MCD</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>McDonald's Corporation Common Stock</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16T20:46:22+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Weston Vs Auburn HS Baseball Playoffs Live Mcdonald's Menu (DNpB6daVUy)</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>0.012</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFAyT3hmdVh6ekN0ZTBpWHk1emRrbGpsMWZhYnlzX21yak1KTGFSaVQtMkE2V1NnUFpxN3I0Zko4MEYxcGJ1N3BTUEE1UWRNOEZGZXJ0RDlCUDkzYTA?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Mshale</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>韋斯頓 vs 奧本高中棒球季後賽現場麥當勞菜單 (DNpB6daVUy)</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>layoff；layoffs</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="3" t="inlineStr">
-        <is>
-          <t>c13b5040b8c70f603e4a60b0</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>9e7bfc6bb20e98ffd15ab1ea</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="inlineStr"/>
-      <c r="AF3" s="3" t="inlineStr"/>
-      <c r="AG3" s="3" t="inlineStr"/>
-      <c r="AH3" s="3" t="inlineStr"/>
-      <c r="AI3" s="3" t="inlineStr"/>
-      <c r="AJ3" s="3" t="inlineStr"/>
-      <c r="AK3" s="3" t="inlineStr"/>
-      <c r="AL3" s="3" t="inlineStr"/>
-      <c r="AM3" s="3" t="inlineStr"/>
-      <c r="AN3" s="3" t="inlineStr"/>
-      <c r="AO3" s="3" t="inlineStr"/>
-      <c r="AP3" s="3" t="inlineStr"/>
-      <c r="AQ3" s="3" t="inlineStr"/>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
-      <c r="AU3" s="3" t="inlineStr"/>
-      <c r="AV3" s="3" t="inlineStr"/>
-      <c r="AW3" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX3" s="3" t="inlineStr"/>
-      <c r="AY3" s="3" t="inlineStr"/>
-      <c r="AZ3" s="3" t="inlineStr"/>
-      <c r="BA3" s="3" t="inlineStr"/>
-      <c r="BB3" s="3" t="inlineStr">
-        <is>
-          <t>MCD</t>
-        </is>
-      </c>
-      <c r="BC3" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD3" s="3" t="inlineStr"/>
-      <c r="BE3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH3" s="3" t="inlineStr"/>
-      <c r="BI3" s="3" t="inlineStr"/>
-      <c r="BJ3" s="3" t="inlineStr"/>
-      <c r="BK3" s="3" t="inlineStr"/>
-      <c r="BL3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>General Motors</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16T20:33:08+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>GM John Lynch eyes big finish for 49ers in wide-open NFC playoff race</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>0.423</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPb1NrMWZULXowOTU5SXJhWFpGTEE4dzhiU0k3Z3hMem1ib1NGenNseGh3QXlBVDVpWDBEN1VuZTItNXR0Y2JoZVoySkFMcUlTWnhGWTBsWmFVYlM0eUdfMGNfYV9HRTFaVWVKNjF6X0ZzenVXdFhHNlVoLXRzWjFBb1U3RTJJdHFCWkE?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>Yahoo Sports</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>總經理約翰林奇 (John Lynch) 希望 49 人隊在 NFC 季後賽中取得優異成績</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>a2cc74f8cb4f2868b11c2b32</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>99167d191e8f9dfaa8138dc3</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr"/>
-      <c r="AF4" s="3" t="inlineStr"/>
-      <c r="AG4" s="3" t="inlineStr"/>
-      <c r="AH4" s="3" t="inlineStr"/>
-      <c r="AI4" s="3" t="inlineStr"/>
-      <c r="AJ4" s="3" t="inlineStr"/>
-      <c r="AK4" s="3" t="inlineStr"/>
-      <c r="AL4" s="3" t="inlineStr"/>
-      <c r="AM4" s="3" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr"/>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="inlineStr"/>
-      <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="3" t="inlineStr"/>
-      <c r="AW4" s="3" t="inlineStr"/>
-      <c r="AX4" s="3" t="inlineStr"/>
-      <c r="AY4" s="3" t="inlineStr"/>
-      <c r="AZ4" s="3" t="inlineStr"/>
-      <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="BC4" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD4" s="3" t="inlineStr"/>
-      <c r="BE4" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF4" s="3" t="inlineStr"/>
-      <c r="BG4" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH4" s="3" t="inlineStr"/>
-      <c r="BI4" s="3" t="inlineStr"/>
-      <c r="BJ4" s="3" t="inlineStr"/>
-      <c r="BK4" s="3" t="inlineStr"/>
-      <c r="BL4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>FSLR</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>First Solar, Inc.</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-16T19:38:27+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>FSLR Stockholders Have Opportunity to Lead First Solar, Inc. Class Action Lawsuit – Contact Bronstein, Gewirtz and Grossman, LLC Today!</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>重大訴訟</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>0.053</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxPYTRpVkpjZkxxY0JlcS1TeUVvaGRDRzUtMzFDMFFGRUZkYjNQMWFLOUVjdjFlNUdsMUNsRE5ZSWhUTHJYcEdNQmxuUFM4TC1PNENMTUQ1WVJDTk9YcmlGY0szRThtdHM3ZXFUVy1BcGhfQnB1RW1zNWtDTHk4ek94MzZ3bzBFbkdZZHFZZzNjMXI4b2FsQXpEUkktMF9iTUVwSWVSMEducmExRGVRS2VvdjBnQllOSmJOcHRkYl8yNlF1c0RCY3E2ckZkWHFBUmtERVgwSHUxT2pIS1VWb1FFZnREa2I?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>ACCESS Newswire</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr">
-        <is>
-          <t>FSLR 股東有機會領導 First Solar, Inc. 集體訴訟 – 立即聯繫 Bronstein、Gewirtz 和 Grossman, LLC！</t>
-        </is>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>MAJOR_LITIGATION</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>class action</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr">
-        <is>
-          <t>fe7f351f050843908b8b3fac725cc668</t>
-        </is>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
-        <is>
-          <t>b1915ec4a2488bc955728b02</t>
-        </is>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>d4cfd68254a8e4063b3c0497</t>
-        </is>
-      </c>
-      <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
-        <is>
-          <t>FSLR</t>
-        </is>
-      </c>
-      <c r="BC5" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD5" s="4" t="inlineStr"/>
-      <c r="BE5" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG5" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH5" s="4" t="inlineStr"/>
-      <c r="BI5" s="4" t="inlineStr"/>
-      <c r="BJ5" s="4" t="inlineStr"/>
-      <c r="BK5" s="4" t="inlineStr">
+      <c r="BK2" s="3" t="inlineStr">
         <is>
           <t>離線覆核</t>
         </is>
       </c>
-      <c r="BL5" s="4" t="inlineStr">
+      <c r="BL2" s="3" t="inlineStr">
         <is>
           <t>2026-10-26T15:42:35.885456+08:00</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>DOW</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Dow Inc. Common Stock </t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16T17:40:29+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Bloomberg Money Minute: Dow Hits Record High As SpaceX Plunges Canada Revenue Agency Data Breaches (Kz5b0Hg4QP)</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>資料外洩</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>0.197</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBTNzRpUEoxUGR0MkdUWkFld0xOblN1SEh1U3VnQWU2dDkyaXVta1NzTUhiRU8ycXlpeXZNUTZCd1N3VmhHLTdPQ1RsdUJvUWNnc2ZfTnpCbEY5a0U?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>Mshale</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="inlineStr">
-        <is>
-          <t>彭博財經紀要：隨著 SpaceX 暴跌，道瓊指數創下歷史新高 加拿大稅務局資料外洩 (Kz5b0Hg4QP)</t>
-        </is>
-      </c>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>CYBER</t>
-        </is>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>DATA_BREACH</t>
-        </is>
-      </c>
-      <c r="Z6" s="3" t="inlineStr">
-        <is>
-          <t>data breach</t>
-        </is>
-      </c>
-      <c r="AA6" s="3" t="inlineStr"/>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="3" t="inlineStr">
-        <is>
-          <t>f2b86040989baf9e42cfee63</t>
-        </is>
-      </c>
-      <c r="AD6" s="3" t="inlineStr">
-        <is>
-          <t>7031ef56aea01413bbc14779</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="inlineStr"/>
-      <c r="AF6" s="3" t="inlineStr"/>
-      <c r="AG6" s="3" t="inlineStr"/>
-      <c r="AH6" s="3" t="inlineStr"/>
-      <c r="AI6" s="3" t="inlineStr"/>
-      <c r="AJ6" s="3" t="inlineStr"/>
-      <c r="AK6" s="3" t="inlineStr"/>
-      <c r="AL6" s="3" t="inlineStr"/>
-      <c r="AM6" s="3" t="inlineStr"/>
-      <c r="AN6" s="3" t="inlineStr"/>
-      <c r="AO6" s="3" t="inlineStr"/>
-      <c r="AP6" s="3" t="inlineStr"/>
-      <c r="AQ6" s="3" t="inlineStr"/>
-      <c r="AR6" s="3" t="inlineStr"/>
-      <c r="AS6" s="3" t="inlineStr"/>
-      <c r="AT6" s="3" t="inlineStr"/>
-      <c r="AU6" s="3" t="inlineStr"/>
-      <c r="AV6" s="3" t="inlineStr"/>
-      <c r="AW6" s="3" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX6" s="3" t="inlineStr"/>
-      <c r="AY6" s="3" t="inlineStr"/>
-      <c r="AZ6" s="3" t="inlineStr"/>
-      <c r="BA6" s="3" t="inlineStr"/>
-      <c r="BB6" s="3" t="inlineStr">
-        <is>
-          <t>DOW</t>
-        </is>
-      </c>
-      <c r="BC6" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD6" s="3" t="inlineStr"/>
-      <c r="BE6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="3" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH6" s="3" t="inlineStr"/>
-      <c r="BI6" s="3" t="inlineStr"/>
-      <c r="BJ6" s="3" t="inlineStr"/>
-      <c r="BK6" s="3" t="inlineStr"/>
-      <c r="BL6" s="3" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Coinbase</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16T16:03:58+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Bitcoin demand weakens as Coinbase premium inde...</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>營運惡化</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>'-0.947</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQczhZLW84MjR0NmNrcVE5LVRvLW1LTm5xMDJxaUl6cXBfbERFV3R1N1ROa0p4RWExbkZuOVJQT19nWV93RWdJamtqNVY2bURoeUFUczdBY2J3eUJEVkhBTkE3dXNaUG9WYzdtVmdJSUhtSDlyRXR6b2JETU9zTVAzdDkyMmNFNTNTSGc?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>Pluang</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr">
-        <is>
-          <t>隨著 Coinbase 溢價指數下降，比特幣需求減弱</t>
-        </is>
-      </c>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>OPERATING_DETERIORATION</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>demand weakens</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr"/>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>dedd5344f34e3e3828bebfeb</t>
-        </is>
-      </c>
-      <c r="AD7" s="3" t="inlineStr">
-        <is>
-          <t>8223eec336e2ca59113293fd</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="inlineStr"/>
-      <c r="AF7" s="3" t="inlineStr"/>
-      <c r="AG7" s="3" t="inlineStr"/>
-      <c r="AH7" s="3" t="inlineStr"/>
-      <c r="AI7" s="3" t="inlineStr"/>
-      <c r="AJ7" s="3" t="inlineStr"/>
-      <c r="AK7" s="3" t="inlineStr"/>
-      <c r="AL7" s="3" t="inlineStr"/>
-      <c r="AM7" s="3" t="inlineStr"/>
-      <c r="AN7" s="3" t="inlineStr"/>
-      <c r="AO7" s="3" t="inlineStr"/>
-      <c r="AP7" s="3" t="inlineStr"/>
-      <c r="AQ7" s="3" t="inlineStr"/>
-      <c r="AR7" s="3" t="inlineStr"/>
-      <c r="AS7" s="3" t="inlineStr"/>
-      <c r="AT7" s="3" t="inlineStr"/>
-      <c r="AU7" s="3" t="inlineStr"/>
-      <c r="AV7" s="3" t="inlineStr"/>
-      <c r="AW7" s="3" t="inlineStr"/>
-      <c r="AX7" s="3" t="inlineStr"/>
-      <c r="AY7" s="3" t="inlineStr"/>
-      <c r="AZ7" s="3" t="inlineStr"/>
-      <c r="BA7" s="3" t="inlineStr"/>
-      <c r="BB7" s="3" t="inlineStr">
-        <is>
-          <t>COIN</t>
-        </is>
-      </c>
-      <c r="BC7" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD7" s="3" t="inlineStr"/>
-      <c r="BE7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF7" s="3" t="inlineStr"/>
-      <c r="BG7" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH7" s="3" t="inlineStr"/>
-      <c r="BI7" s="3" t="inlineStr"/>
-      <c r="BJ7" s="3" t="inlineStr"/>
-      <c r="BK7" s="3" t="inlineStr"/>
-      <c r="BL7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Boeing</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16T15:24:44+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>Stewart Cink beats Miguel Angel Jiménez in playoff to win Boeing Classic, earns fifth title of season</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>0.243</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi8wFBVV95cUxOaUFhMGUxRXNPeDVmVjV2ajd5Y0VEMHQ3X3E1QVdkLWZYMnpOSjdqX281SjdCYmhkdXpRc1hSRXVoSkdweWs5OXVNa1NENHNpdWVWS25falJkM2FfcC1fUGR3alJKQ0R0QlU4eTFwZ0RVcVFFV1RqWkl5ZWNoV1dYZG1OeGRuZ05JUE11Q2ZjeHVhck8wRzFROFRHdGZIM0VKQ1Ytc2N0a0w0S0QzZlVEMWlnckVTRXFSQmNxZk8xU01NbDBnTE5OUUlIaU9KNFdBT3dPWW5Kb0lxdnZhX1RtR1REeWk2VG5qSDlyUDdrRFVtWHM?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t>PGA Tour</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t>史都華辛克在延長賽中擊敗米格爾安赫爾希門尼斯贏得波音精英賽冠軍，贏得本賽季第五個冠軍</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA8" s="3" t="inlineStr"/>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="3" t="inlineStr">
-        <is>
-          <t>b17bd1aca568811c85b8e436</t>
-        </is>
-      </c>
-      <c r="AD8" s="3" t="inlineStr">
-        <is>
-          <t>f2ba7dc9e87612963ae7af5e</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="inlineStr"/>
-      <c r="AF8" s="3" t="inlineStr"/>
-      <c r="AG8" s="3" t="inlineStr"/>
-      <c r="AH8" s="3" t="inlineStr"/>
-      <c r="AI8" s="3" t="inlineStr"/>
-      <c r="AJ8" s="3" t="inlineStr"/>
-      <c r="AK8" s="3" t="inlineStr"/>
-      <c r="AL8" s="3" t="inlineStr"/>
-      <c r="AM8" s="3" t="inlineStr"/>
-      <c r="AN8" s="3" t="inlineStr"/>
-      <c r="AO8" s="3" t="inlineStr"/>
-      <c r="AP8" s="3" t="inlineStr"/>
-      <c r="AQ8" s="3" t="inlineStr"/>
-      <c r="AR8" s="3" t="inlineStr"/>
-      <c r="AS8" s="3" t="inlineStr"/>
-      <c r="AT8" s="3" t="inlineStr"/>
-      <c r="AU8" s="3" t="inlineStr"/>
-      <c r="AV8" s="3" t="inlineStr"/>
-      <c r="AW8" s="3" t="inlineStr"/>
-      <c r="AX8" s="3" t="inlineStr"/>
-      <c r="AY8" s="3" t="inlineStr"/>
-      <c r="AZ8" s="3" t="inlineStr"/>
-      <c r="BA8" s="3" t="inlineStr"/>
-      <c r="BB8" s="3" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="BC8" s="3" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD8" s="3" t="inlineStr"/>
-      <c r="BE8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF8" s="3" t="inlineStr"/>
-      <c r="BG8" s="3" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH8" s="3" t="inlineStr"/>
-      <c r="BI8" s="3" t="inlineStr"/>
-      <c r="BJ8" s="3" t="inlineStr"/>
-      <c r="BK8" s="3" t="inlineStr"/>
-      <c r="BL8" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL8"/>
+  <autoFilter ref="A1:BL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13379,7 +12623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL12"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13770,1934 +13014,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Regency Centers</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16T23:27:57+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>NPP Reg. Executive elections: Incumbent Bukari secures landslide mandate, vows 2028 unity victory</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1CTV9KdFR5Njd5NVJVWTE3b04xS2NPSk0ydWltaEt3X29kU3lmZkJXRWxYVGtacEs1UzhGWklUcHFlZ0RDb2lpdmFOWW9ZYl9DaEJtUmFLcElmbTRqaTA2Mk1EM2TSAVxBVV95cUxQWmJ3b1U2MmZLZ1RTYVF4R2FDLVJsTVZJc2tqdkt6UmFMTjZhTFJiaURQM2RZMngyX1UwVkdSOGxmdS1HSzhlaVcxQk1jeWROeEFISzlmYWlkVmJPZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>modernghana.com</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>核電廠註冊行政選舉：現任布卡里獲得壓倒性授權，誓言 2028 年團結勝利</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>landslide</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>be6948fe80f28d89445238d5</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>1d6bf176ccf77d1e7eafac50</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>REG</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>REG</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Visa Inc.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16T23:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>San Jose Earthquakes v Minnesota Utd Odds</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>0.023</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxQMlA0R0RKTHlFbW0tZ043eUlvb2lOOGE4eDRXN2FMaGV6Y3htYmt0a25kV1BuTTh3ODNpM2p5bTl4c3NaQ2dBeDYzU0d5dHpCdm1HT3RncjJPNFh3bXJPWnJabDd6YkhJOTNLWDdpd0JVTUQ2RV9LYWtObmZ3cUJQU1d0Tmlqc2JCSjZpMHRmd2t6a3BR?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>FanDuel Sportsbook</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>聖荷西地震 v 明尼蘇達聯隊 賠率</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>earthquake</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>91cf89d412caaf51c29ef7fe</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>cc3b8159b78e38bc3746eab0</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr"/>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="BC3" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="2" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="BE3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="2" t="inlineStr"/>
-      <c r="BH3" s="2" t="inlineStr"/>
-      <c r="BI3" s="2" t="inlineStr"/>
-      <c r="BJ3" s="2" t="inlineStr"/>
-      <c r="BK3" s="2" t="inlineStr"/>
-      <c r="BL3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Brown &amp; Brown</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-16T22:48:27+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>SANTOS FC Vs CSD MACARA LIVE Watchalong | Copa Sudamericana 2026 | UH Bro Sorteggio Playoff Serie C (hzm5f9zfLk)</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>裁員或人力縮減</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>0.118</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr"/>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9YanZhOWFhX1BLaFlpVDFpUXpBbWNBdUZXUWlhOE1TMC1TcGw0WkhzM3FnaFJFMmxxWUtDN0pHc2F3eEpSZ3A2OEhRUVlHRWJDTEpCQmh0akZQd2s?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t>Mshale</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
-        <is>
-          <t>SANTOS FC 對 CSD MACARA 直播觀看 | 2026 年南美杯 |呃 Bro Sorteggio 季後賽意丙 (hzm5f9zfLk)</t>
-        </is>
-      </c>
-      <c r="X4" s="3" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>WORKFORCE_REDUCTION</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>layoff</t>
-        </is>
-      </c>
-      <c r="AA4" s="3" t="inlineStr"/>
-      <c r="AB4" s="3" t="inlineStr"/>
-      <c r="AC4" s="3" t="inlineStr">
-        <is>
-          <t>b4b729190f5cda4073e80344</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>6ee96ffb0e538de9b81fb7b7</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="inlineStr"/>
-      <c r="AF4" s="3" t="inlineStr"/>
-      <c r="AG4" s="3" t="inlineStr"/>
-      <c r="AH4" s="3" t="inlineStr"/>
-      <c r="AI4" s="3" t="inlineStr"/>
-      <c r="AJ4" s="3" t="inlineStr"/>
-      <c r="AK4" s="3" t="inlineStr"/>
-      <c r="AL4" s="3" t="inlineStr"/>
-      <c r="AM4" s="3" t="inlineStr"/>
-      <c r="AN4" s="3" t="inlineStr"/>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP4" s="3" t="inlineStr"/>
-      <c r="AQ4" s="3" t="inlineStr"/>
-      <c r="AR4" s="3" t="inlineStr"/>
-      <c r="AS4" s="3" t="inlineStr"/>
-      <c r="AT4" s="3" t="inlineStr"/>
-      <c r="AU4" s="3" t="inlineStr"/>
-      <c r="AV4" s="3" t="inlineStr"/>
-      <c r="AW4" s="3" t="inlineStr"/>
-      <c r="AX4" s="3" t="inlineStr"/>
-      <c r="AY4" s="3" t="inlineStr"/>
-      <c r="AZ4" s="3" t="inlineStr"/>
-      <c r="BA4" s="3" t="inlineStr"/>
-      <c r="BB4" s="3" t="inlineStr">
-        <is>
-          <t>BRO</t>
-        </is>
-      </c>
-      <c r="BC4" s="3" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD4" s="3" t="inlineStr">
-        <is>
-          <t>BRO</t>
-        </is>
-      </c>
-      <c r="BE4" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG4" s="3" t="inlineStr"/>
-      <c r="BH4" s="3" t="inlineStr"/>
-      <c r="BI4" s="3" t="inlineStr"/>
-      <c r="BJ4" s="3" t="inlineStr"/>
-      <c r="BK4" s="3" t="inlineStr"/>
-      <c r="BL4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Estée Lauder Companies (The)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16T20:41:00+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>El Niño keeps Atlantic hurricane activity unusually quiet</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>'-0.844</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxONUdoVEFFZ0NxZlJYaGp2QzhlWHhORGcybmFrTE5VQWlCaGFDdHpQXzVsU056enZzWHhNbE9USVIwRkhsZmJDUzdlVFZ1R2lCSW1ZeFN0VDJtVzQyc0Y1NHJFa2Izb1ZhSWxRcWFoQUNETXVrUlBsXy1xdTN4NTFkVzRsVEN4bGo3N2ZpaFRhTTN0UFp6?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>fpren.org</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>厄爾尼諾現象使大西洋颶風活動異常平靜</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t>hurricane</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>97b78f72c6b4bb3bd00b1f0f</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>19636fc6066b4628a348e767</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
-      <c r="AG5" s="2" t="inlineStr"/>
-      <c r="AH5" s="2" t="inlineStr"/>
-      <c r="AI5" s="2" t="inlineStr"/>
-      <c r="AJ5" s="2" t="inlineStr"/>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr"/>
-      <c r="AM5" s="2" t="inlineStr"/>
-      <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP5" s="2" t="inlineStr"/>
-      <c r="AQ5" s="2" t="inlineStr"/>
-      <c r="AR5" s="2" t="inlineStr"/>
-      <c r="AS5" s="2" t="inlineStr"/>
-      <c r="AT5" s="2" t="inlineStr"/>
-      <c r="AU5" s="2" t="inlineStr"/>
-      <c r="AV5" s="2" t="inlineStr"/>
-      <c r="AW5" s="2" t="inlineStr"/>
-      <c r="AX5" s="2" t="inlineStr"/>
-      <c r="AY5" s="2" t="inlineStr"/>
-      <c r="AZ5" s="2" t="inlineStr"/>
-      <c r="BA5" s="2" t="inlineStr"/>
-      <c r="BB5" s="2" t="inlineStr">
-        <is>
-          <t>EL</t>
-        </is>
-      </c>
-      <c r="BC5" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD5" s="2" t="inlineStr">
-        <is>
-          <t>EL</t>
-        </is>
-      </c>
-      <c r="BE5" s="2" t="inlineStr"/>
-      <c r="BF5" s="2" t="inlineStr"/>
-      <c r="BG5" s="2" t="inlineStr"/>
-      <c r="BH5" s="2" t="inlineStr"/>
-      <c r="BI5" s="2" t="inlineStr"/>
-      <c r="BJ5" s="2" t="inlineStr"/>
-      <c r="BK5" s="2" t="inlineStr"/>
-      <c r="BL5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>NiSource</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16T20:35:00+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Kagwe assures Kenyans of food security despite drought threat ni</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr"/>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQNWR1eEhCSmZ6SHJLMjBUN2N2WXB1SzhFcGE1WElNRVdjekc5WjU2NmdVbktTN2NkTVgtVjlBUkNOQzdMaUFoZGc3aWJyZWFPZDVFcmQwc0E5V2RvNWl5REwtQ0lMaWpRQ00wVDdjY01wV1JlSGk3ZEdsYnVGdkZhTmxFZ1VNUlVVVWdFWlVMNGJlSFU2UW9USnJGNzl0QktNeGZFUjFHQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>the-star.co.ke</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>卡格威向肯亞人民保證糧食安全，儘管面臨乾旱威脅</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z6" s="2" t="inlineStr">
-        <is>
-          <t>drought</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>4250021e34bc480c898f53db</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr">
-        <is>
-          <t>53ab3950961552478d4c57b4</t>
-        </is>
-      </c>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr"/>
-      <c r="AI6" s="2" t="inlineStr"/>
-      <c r="AJ6" s="2" t="inlineStr"/>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP6" s="2" t="inlineStr"/>
-      <c r="AQ6" s="2" t="inlineStr"/>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr"/>
-      <c r="AT6" s="2" t="inlineStr"/>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr"/>
-      <c r="AW6" s="2" t="inlineStr"/>
-      <c r="AX6" s="2" t="inlineStr"/>
-      <c r="AY6" s="2" t="inlineStr"/>
-      <c r="AZ6" s="2" t="inlineStr"/>
-      <c r="BA6" s="2" t="inlineStr"/>
-      <c r="BB6" s="2" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="BC6" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD6" s="2" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="BE6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG6" s="2" t="inlineStr"/>
-      <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
-      <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Consolidated Edison</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16T18:10:56+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>HDOT Director Ed Sniffen gives update on closures, road conditions affected by Hurricane Lala</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>'-0.421</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxOQUxtVzhINjRUTXY5SzFmMzBfX2g3YUk1QVdDQk5zcjh6bTJNUDF5QklHQ0hwYmU2cmJqVUpIbG1rUkRyaklQeUZURUZkR3JmWWp3RDNoX1dhd2ZOVWFlRXkwenY3TW5PVFRsQzVHcVlBaWpobFpRUDkxQXlTOGNpbWN0aUVhalotYWtaRFliU3dqSGcxMC0zR08tLXI5d2ZYaDFTMkQzYWNTNURMQ3htb3V0UGt5RXBTNDhHSzdzVFJuRkZxUWdJeWVMRlNyRnc5TndN?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Hawaii News Now</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>HDOT 總監 Ed Sniffen 介紹了受颶風拉拉影響的封閉和路況的最新情況</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z7" s="2" t="inlineStr">
-        <is>
-          <t>hurricane</t>
-        </is>
-      </c>
-      <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>875f1b9415924987a9bf94b9</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr">
-        <is>
-          <t>7a65afbf862208aec0e28d40</t>
-        </is>
-      </c>
-      <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr"/>
-      <c r="AG7" s="2" t="inlineStr"/>
-      <c r="AH7" s="2" t="inlineStr"/>
-      <c r="AI7" s="2" t="inlineStr"/>
-      <c r="AJ7" s="2" t="inlineStr"/>
-      <c r="AK7" s="2" t="inlineStr"/>
-      <c r="AL7" s="2" t="inlineStr"/>
-      <c r="AM7" s="2" t="inlineStr"/>
-      <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP7" s="2" t="inlineStr"/>
-      <c r="AQ7" s="2" t="inlineStr"/>
-      <c r="AR7" s="2" t="inlineStr"/>
-      <c r="AS7" s="2" t="inlineStr"/>
-      <c r="AT7" s="2" t="inlineStr"/>
-      <c r="AU7" s="2" t="inlineStr"/>
-      <c r="AV7" s="2" t="inlineStr"/>
-      <c r="AW7" s="2" t="inlineStr"/>
-      <c r="AX7" s="2" t="inlineStr"/>
-      <c r="AY7" s="2" t="inlineStr"/>
-      <c r="AZ7" s="2" t="inlineStr"/>
-      <c r="BA7" s="2" t="inlineStr"/>
-      <c r="BB7" s="2" t="inlineStr">
-        <is>
-          <t>ED</t>
-        </is>
-      </c>
-      <c r="BC7" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD7" s="2" t="inlineStr">
-        <is>
-          <t>ED</t>
-        </is>
-      </c>
-      <c r="BE7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG7" s="2" t="inlineStr"/>
-      <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
-      <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Realty Income</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16T16:56:17+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>City urges residents to stay safe as Hurricane Lala passes O‘ahu; TheBus service temporarily suspended due to extreme weather</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>'-0.917</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNQm1BZVJCYjVZajJsTEtXeFFXVU93Y2NpQ1cwbWhiN3l5d2tpNERrdF9vVUUwV0t2cE92dnd2NVJQRzZyN2xsVEQ5emtpNXlBNTNMX1B6cnAzM3F1bndYNTZfY0s2T3JmSGdYTHlDRmx3WnNhbWc4Yl90ek5rcmpqbW1NQWJ4WTF1aS1INU1HMjJpZF9aRGpsTkQxRUVTNVZUV0hBc2NmeVpOZnJjM3h3ZkM1Z2hEaldEWW5vTVdYNHhtZDVVZFp4Vm9KUzhaSzV2bWpMek5TMkZiNURnbzE3SlNRWnMxWW9kaUF3?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>City and County of Honolulu (.gov)</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>颶風拉拉經過歐胡島時，市政府敦促居民保持安全；巴士服務因極端天氣而暫停</t>
-        </is>
-      </c>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="inlineStr">
-        <is>
-          <t>hurricane</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
-      <c r="AC8" s="2" t="inlineStr">
-        <is>
-          <t>ba3d714f5b7b6e88b252e3bc</t>
-        </is>
-      </c>
-      <c r="AD8" s="2" t="inlineStr">
-        <is>
-          <t>a2f6a7d1a9837b498c452ac1</t>
-        </is>
-      </c>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
-      <c r="AG8" s="2" t="inlineStr"/>
-      <c r="AH8" s="2" t="inlineStr"/>
-      <c r="AI8" s="2" t="inlineStr"/>
-      <c r="AJ8" s="2" t="inlineStr"/>
-      <c r="AK8" s="2" t="inlineStr"/>
-      <c r="AL8" s="2" t="inlineStr"/>
-      <c r="AM8" s="2" t="inlineStr"/>
-      <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP8" s="2" t="inlineStr"/>
-      <c r="AQ8" s="2" t="inlineStr"/>
-      <c r="AR8" s="2" t="inlineStr"/>
-      <c r="AS8" s="2" t="inlineStr"/>
-      <c r="AT8" s="2" t="inlineStr"/>
-      <c r="AU8" s="2" t="inlineStr"/>
-      <c r="AV8" s="2" t="inlineStr"/>
-      <c r="AW8" s="2" t="inlineStr"/>
-      <c r="AX8" s="2" t="inlineStr"/>
-      <c r="AY8" s="2" t="inlineStr"/>
-      <c r="AZ8" s="2" t="inlineStr"/>
-      <c r="BA8" s="2" t="inlineStr"/>
-      <c r="BB8" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="BC8" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD8" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="BE8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG8" s="2" t="inlineStr"/>
-      <c r="BH8" s="2" t="inlineStr"/>
-      <c r="BI8" s="2" t="inlineStr"/>
-      <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Estée Lauder Companies (The)</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16T08:49:52+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>ABC-7 First Alert: Flash Flood Warning for East El Paso County including Far East El Paso, Homestead Meadows, and Montana Vista until 8:30 PM</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>'-0.033</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikAJBVV95cUxNa0xheUhaS1dWSzFZS0NXbUwyNS03YlkzRnd2ZXo3bW1LM3huUjZUdDRncG9LY0lHVEFKeFFHSTFzbkRtcElKQ2tzZjl6V1pXOVUyenJ6UGlVTXdsc0VqamhrWFBkUW9pZFBtSk9VRzJxbmRGVGJpRU8xaEE0SlMzanNDMmI2RjUzQ2FqX3dNWWN5emduYk5GbXlVUHI1UW13ZkJST1ZTT015LUZIWmp2VVFnemE5dkU5MGltN3RWeXdFUW0xUWptXy1RMkZ6am5jaERwTE5fMC05ZmlsMFZwdlU2aGVXOVQ1MzhqX2o0aFZ0V3J3Ti1kUkUxTHN4MDdsR1ZMNFBTSVhQR1hSRjh1Sw?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>KVIA</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>ABC-7 第一個警報：東埃爾帕索縣（包括遠東埃爾帕索、Homestead Meadows 和 Montana Vista）的山洪警報持續至晚上 8:30</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>flood</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>682286533d48fb779fb80365</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="inlineStr">
-        <is>
-          <t>fa5aacad9656034ff5017b50</t>
-        </is>
-      </c>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
-      <c r="AG9" s="2" t="inlineStr"/>
-      <c r="AH9" s="2" t="inlineStr"/>
-      <c r="AI9" s="2" t="inlineStr"/>
-      <c r="AJ9" s="2" t="inlineStr"/>
-      <c r="AK9" s="2" t="inlineStr"/>
-      <c r="AL9" s="2" t="inlineStr"/>
-      <c r="AM9" s="2" t="inlineStr"/>
-      <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP9" s="2" t="inlineStr"/>
-      <c r="AQ9" s="2" t="inlineStr"/>
-      <c r="AR9" s="2" t="inlineStr"/>
-      <c r="AS9" s="2" t="inlineStr"/>
-      <c r="AT9" s="2" t="inlineStr"/>
-      <c r="AU9" s="2" t="inlineStr"/>
-      <c r="AV9" s="2" t="inlineStr"/>
-      <c r="AW9" s="2" t="inlineStr"/>
-      <c r="AX9" s="2" t="inlineStr"/>
-      <c r="AY9" s="2" t="inlineStr"/>
-      <c r="AZ9" s="2" t="inlineStr"/>
-      <c r="BA9" s="2" t="inlineStr"/>
-      <c r="BB9" s="2" t="inlineStr">
-        <is>
-          <t>EL</t>
-        </is>
-      </c>
-      <c r="BC9" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD9" s="2" t="inlineStr">
-        <is>
-          <t>EL</t>
-        </is>
-      </c>
-      <c r="BE9" s="2" t="inlineStr"/>
-      <c r="BF9" s="2" t="inlineStr"/>
-      <c r="BG9" s="2" t="inlineStr"/>
-      <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
-      <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Realty Income</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16T05:07:01+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>City opens eight hurricane refuge areas as O‘ahu prepares for Hurricane Lala</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0.473</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr"/>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxQUjluY3habHN4T0JhdktCMDA5WG1xaE9RYWlqZUxWLVdJMlg0dTZDYThfNFFNMTVnUEFFRjRBc2tZTl9DcFQ4Z1VqQS1KTURXQnhhMGpnY0xkdThzZWdwOWRBMVFQM0NyNENxSmZSNGZlSFRDcUxtT0tsVXhESS1xQ0J6djRHc0FpcjFib09XVktnNFEwcXI5anJBVTlYVUprRU4yRm1QVDBHcUU?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>honolulu.gov</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>歐胡島為颶風拉拉做準備，市政府開放了八個颶風避難區</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z10" s="2" t="inlineStr">
-        <is>
-          <t>hurricane</t>
-        </is>
-      </c>
-      <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>1986a3c39c42d432ef952936</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr">
-        <is>
-          <t>64fa53d0c7056eec4552ea93</t>
-        </is>
-      </c>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
-      <c r="AG10" s="2" t="inlineStr"/>
-      <c r="AH10" s="2" t="inlineStr"/>
-      <c r="AI10" s="2" t="inlineStr"/>
-      <c r="AJ10" s="2" t="inlineStr"/>
-      <c r="AK10" s="2" t="inlineStr"/>
-      <c r="AL10" s="2" t="inlineStr"/>
-      <c r="AM10" s="2" t="inlineStr"/>
-      <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP10" s="2" t="inlineStr"/>
-      <c r="AQ10" s="2" t="inlineStr"/>
-      <c r="AR10" s="2" t="inlineStr"/>
-      <c r="AS10" s="2" t="inlineStr"/>
-      <c r="AT10" s="2" t="inlineStr"/>
-      <c r="AU10" s="2" t="inlineStr"/>
-      <c r="AV10" s="2" t="inlineStr"/>
-      <c r="AW10" s="2" t="inlineStr"/>
-      <c r="AX10" s="2" t="inlineStr"/>
-      <c r="AY10" s="2" t="inlineStr"/>
-      <c r="AZ10" s="2" t="inlineStr"/>
-      <c r="BA10" s="2" t="inlineStr"/>
-      <c r="BB10" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="BC10" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD10" s="2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="BE10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG10" s="2" t="inlineStr"/>
-      <c r="BH10" s="2" t="inlineStr"/>
-      <c r="BI10" s="2" t="inlineStr"/>
-      <c r="BJ10" s="2" t="inlineStr"/>
-      <c r="BK10" s="2" t="inlineStr"/>
-      <c r="BL10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Lowe's</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16T04:26:30+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>US trade court rules Trump may eliminate tariff exemption for low-cost imports</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>關稅</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>'-0.068</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPajUwZ0VwQTI3d3AtNVJaankweDZFX21iYThTb2hpUjBKWTZjSFJOME50R2hKLUhvazFSWFAwOXVGMmF0WVBocG94NjFjcWtSUmZVX0dsR2FHeFJfbVlfRVdiX0g0cHNEOVBoZE9JcFdxUFpHOTkwYmM1cWNfWXg3YTQ3WHhPOTJpeFMtOFBhRHhUSzdxZkNLWHU4bVFDN19Ga0pXRFZlbDBud1E2bHhLVFMwWlJzUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Jurist.org</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>美國貿易法庭裁定川普可能取消低成本進口商品的關稅豁免</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t>GEOPOLITICAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t>TARIFF</t>
-        </is>
-      </c>
-      <c r="Z11" s="2" t="inlineStr">
-        <is>
-          <t>tariff</t>
-        </is>
-      </c>
-      <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
-      <c r="AC11" s="2" t="inlineStr">
-        <is>
-          <t>2b786e797103f1c9cea4665b</t>
-        </is>
-      </c>
-      <c r="AD11" s="2" t="inlineStr">
-        <is>
-          <t>254238fa27fa23e243dca4e8</t>
-        </is>
-      </c>
-      <c r="AE11" s="2" t="inlineStr"/>
-      <c r="AF11" s="2" t="inlineStr"/>
-      <c r="AG11" s="2" t="inlineStr"/>
-      <c r="AH11" s="2" t="inlineStr"/>
-      <c r="AI11" s="2" t="inlineStr"/>
-      <c r="AJ11" s="2" t="inlineStr"/>
-      <c r="AK11" s="2" t="inlineStr"/>
-      <c r="AL11" s="2" t="inlineStr"/>
-      <c r="AM11" s="2" t="inlineStr"/>
-      <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP11" s="2" t="inlineStr"/>
-      <c r="AQ11" s="2" t="inlineStr"/>
-      <c r="AR11" s="2" t="inlineStr"/>
-      <c r="AS11" s="2" t="inlineStr"/>
-      <c r="AT11" s="2" t="inlineStr"/>
-      <c r="AU11" s="2" t="inlineStr"/>
-      <c r="AV11" s="2" t="inlineStr"/>
-      <c r="AW11" s="2" t="inlineStr"/>
-      <c r="AX11" s="2" t="inlineStr"/>
-      <c r="AY11" s="2" t="inlineStr"/>
-      <c r="AZ11" s="2" t="inlineStr"/>
-      <c r="BA11" s="2" t="inlineStr"/>
-      <c r="BB11" s="2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="BC11" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD11" s="2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="BE11" s="2" t="inlineStr"/>
-      <c r="BF11" s="2" t="inlineStr"/>
-      <c r="BG11" s="2" t="inlineStr"/>
-      <c r="BH11" s="2" t="inlineStr"/>
-      <c r="BI11" s="2" t="inlineStr"/>
-      <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Costco</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-16T04:26:30+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>US trade court rules Trump may eliminate tariff exemption for low-cost imports</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>關稅</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>'-0.068</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr"/>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPajUwZ0VwQTI3d3AtNVJaankweDZFX21iYThTb2hpUjBKWTZjSFJOME50R2hKLUhvazFSWFAwOXVGMmF0WVBocG94NjFjcWtSUmZVX0dsR2FHeFJfbVlfRVdiX0g0cHNEOVBoZE9JcFdxUFpHOTkwYmM1cWNfWXg3YTQ3WHhPOTJpeFMtOFBhRHhUSzdxZkNLWHU4bVFDN19Ga0pXRFZlbDBud1E2bHhLVFMwWlJzUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Jurist.org</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>美國貿易法庭裁定川普可能取消低成本進口商品的關稅豁免</t>
-        </is>
-      </c>
-      <c r="X12" s="2" t="inlineStr">
-        <is>
-          <t>GEOPOLITICAL</t>
-        </is>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
-        <is>
-          <t>TARIFF</t>
-        </is>
-      </c>
-      <c r="Z12" s="2" t="inlineStr">
-        <is>
-          <t>tariff</t>
-        </is>
-      </c>
-      <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>2b786e797103f1c9cea4665b</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="inlineStr">
-        <is>
-          <t>bd7ba05d43bd78aab951ded2</t>
-        </is>
-      </c>
-      <c r="AE12" s="2" t="inlineStr"/>
-      <c r="AF12" s="2" t="inlineStr"/>
-      <c r="AG12" s="2" t="inlineStr"/>
-      <c r="AH12" s="2" t="inlineStr"/>
-      <c r="AI12" s="2" t="inlineStr"/>
-      <c r="AJ12" s="2" t="inlineStr"/>
-      <c r="AK12" s="2" t="inlineStr"/>
-      <c r="AL12" s="2" t="inlineStr"/>
-      <c r="AM12" s="2" t="inlineStr"/>
-      <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP12" s="2" t="inlineStr"/>
-      <c r="AQ12" s="2" t="inlineStr"/>
-      <c r="AR12" s="2" t="inlineStr"/>
-      <c r="AS12" s="2" t="inlineStr"/>
-      <c r="AT12" s="2" t="inlineStr"/>
-      <c r="AU12" s="2" t="inlineStr"/>
-      <c r="AV12" s="2" t="inlineStr"/>
-      <c r="AW12" s="2" t="inlineStr"/>
-      <c r="AX12" s="2" t="inlineStr"/>
-      <c r="AY12" s="2" t="inlineStr"/>
-      <c r="AZ12" s="2" t="inlineStr"/>
-      <c r="BA12" s="2" t="inlineStr"/>
-      <c r="BB12" s="2" t="inlineStr">
-        <is>
-          <t>COST</t>
-        </is>
-      </c>
-      <c r="BC12" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD12" s="2" t="inlineStr">
-        <is>
-          <t>COST</t>
-        </is>
-      </c>
-      <c r="BE12" s="2" t="inlineStr"/>
-      <c r="BF12" s="2" t="inlineStr"/>
-      <c r="BG12" s="2" t="inlineStr"/>
-      <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr"/>
-      <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL12"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-08-16.xlsx
+++ b/news_daily/2026-08-16.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$61</definedName>
@@ -27,16 +27,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -61,7 +58,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -69,21 +66,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4747,10 +4736,14 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>AppLovin</t>
+          <t>Apple Inc.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -4915,7 +4908,7 @@
       <c r="BH23" s="2" t="inlineStr"/>
       <c r="BI23" s="2" t="inlineStr">
         <is>
-          <t>Action|Event_Code|Level|事件中文</t>
+          <t>Action|Company|Event_Code|Level|Ticker|事件中文</t>
         </is>
       </c>
       <c r="BJ23" s="2" t="inlineStr"/>

--- a/news_daily/2026-08-16.xlsx
+++ b/news_daily/2026-08-16.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$61</definedName>
@@ -27,13 +27,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -58,7 +61,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -66,13 +69,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1653,28 +1664,32 @@
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1718,7 +1733,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1727,7 +1742,11 @@
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>3a74bc51409c4a16abb3a8dbea5c8dc9</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
           <t>4bdda951eb6a6aa60bcb5524</t>
@@ -1748,7 +1767,11 @@
       <c r="AL6" s="2" t="inlineStr"/>
       <c r="AM6" s="2" t="inlineStr"/>
       <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP6" s="2" t="inlineStr"/>
       <c r="AQ6" s="2" t="inlineStr"/>
       <c r="AR6" s="2" t="inlineStr"/>
@@ -1792,10 +1815,22 @@
         </is>
       </c>
       <c r="BH6" s="2" t="inlineStr"/>
-      <c r="BI6" s="2" t="inlineStr"/>
+      <c r="BI6" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ6" s="2" t="inlineStr"/>
-      <c r="BK6" s="2" t="inlineStr"/>
-      <c r="BL6" s="2" t="inlineStr"/>
+      <c r="BK6" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1831,28 +1866,32 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1896,7 +1935,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1905,7 +1944,11 @@
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>498e3fe130d34714959199b032532463</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>110226387d3b12b339af8926</t>
@@ -1926,7 +1969,11 @@
       <c r="AL7" s="2" t="inlineStr"/>
       <c r="AM7" s="2" t="inlineStr"/>
       <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP7" s="2" t="inlineStr"/>
       <c r="AQ7" s="2" t="inlineStr"/>
       <c r="AR7" s="2" t="inlineStr"/>
@@ -1970,10 +2017,22 @@
         </is>
       </c>
       <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2203,28 +2262,32 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2268,7 +2331,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -2277,7 +2340,11 @@
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>93b750f7413b47468bc7a983bb53d783</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>db4583d6dd240b806b8eb535</t>
@@ -2298,7 +2365,11 @@
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="2" t="inlineStr"/>
       <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
@@ -2342,10 +2413,22 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2575,28 +2658,32 @@
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2640,7 +2727,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -2649,7 +2736,11 @@
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>c676b8a56b984b0f81a01343ec844d72</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
           <t>27142643782a40633e950c45</t>
@@ -2670,7 +2761,11 @@
       <c r="AL11" s="2" t="inlineStr"/>
       <c r="AM11" s="2" t="inlineStr"/>
       <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP11" s="2" t="inlineStr"/>
       <c r="AQ11" s="2" t="inlineStr"/>
       <c r="AR11" s="2" t="inlineStr"/>
@@ -2706,10 +2801,22 @@
         </is>
       </c>
       <c r="BH11" s="2" t="inlineStr"/>
-      <c r="BI11" s="2" t="inlineStr"/>
+      <c r="BI11" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ11" s="2" t="inlineStr"/>
-      <c r="BK11" s="2" t="inlineStr"/>
-      <c r="BL11" s="2" t="inlineStr"/>
+      <c r="BK11" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2745,28 +2852,32 @@
       <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2810,7 +2921,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -2819,7 +2930,11 @@
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>cebebe318e07401fabd08110a904157d</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
           <t>f32e05d4fee7e5f9b3a3d163</t>
@@ -2840,7 +2955,11 @@
       <c r="AL12" s="2" t="inlineStr"/>
       <c r="AM12" s="2" t="inlineStr"/>
       <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP12" s="2" t="inlineStr"/>
       <c r="AQ12" s="2" t="inlineStr"/>
       <c r="AR12" s="2" t="inlineStr"/>
@@ -2884,10 +3003,22 @@
         </is>
       </c>
       <c r="BH12" s="2" t="inlineStr"/>
-      <c r="BI12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ12" s="2" t="inlineStr"/>
-      <c r="BK12" s="2" t="inlineStr"/>
-      <c r="BL12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2923,28 +3054,32 @@
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2988,7 +3123,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2997,7 +3132,11 @@
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr"/>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>8888bd210d52463893d343863d7f37d1</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
           <t>e31e963d51568c648f005502</t>
@@ -3018,7 +3157,11 @@
       <c r="AL13" s="2" t="inlineStr"/>
       <c r="AM13" s="2" t="inlineStr"/>
       <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP13" s="2" t="inlineStr"/>
       <c r="AQ13" s="2" t="inlineStr"/>
       <c r="AR13" s="2" t="inlineStr"/>
@@ -3054,10 +3197,22 @@
         </is>
       </c>
       <c r="BH13" s="2" t="inlineStr"/>
-      <c r="BI13" s="2" t="inlineStr"/>
+      <c r="BI13" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ13" s="2" t="inlineStr"/>
-      <c r="BK13" s="2" t="inlineStr"/>
-      <c r="BL13" s="2" t="inlineStr"/>
+      <c r="BK13" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3093,28 +3248,32 @@
       <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3158,7 +3317,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -3167,7 +3326,11 @@
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr"/>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>8ffe55bf8a104f2c9c0ed244eee7e14a</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
           <t>5eeaa34fe0f6eead25f0c4e7</t>
@@ -3188,7 +3351,11 @@
       <c r="AL14" s="2" t="inlineStr"/>
       <c r="AM14" s="2" t="inlineStr"/>
       <c r="AN14" s="2" t="inlineStr"/>
-      <c r="AO14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP14" s="2" t="inlineStr"/>
       <c r="AQ14" s="2" t="inlineStr"/>
       <c r="AR14" s="2" t="inlineStr"/>
@@ -3224,10 +3391,22 @@
         </is>
       </c>
       <c r="BH14" s="2" t="inlineStr"/>
-      <c r="BI14" s="2" t="inlineStr"/>
+      <c r="BI14" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ14" s="2" t="inlineStr"/>
-      <c r="BK14" s="2" t="inlineStr"/>
-      <c r="BL14" s="2" t="inlineStr"/>
+      <c r="BK14" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3263,28 +3442,32 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3328,7 +3511,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -3337,7 +3520,11 @@
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>8767fdffebe14bb0ab34e4e141dc81a3</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
           <t>516e6b68a635953bfafa0114</t>
@@ -3358,7 +3545,11 @@
       <c r="AL15" s="2" t="inlineStr"/>
       <c r="AM15" s="2" t="inlineStr"/>
       <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP15" s="2" t="inlineStr"/>
       <c r="AQ15" s="2" t="inlineStr"/>
       <c r="AR15" s="2" t="inlineStr"/>
@@ -3394,10 +3585,22 @@
         </is>
       </c>
       <c r="BH15" s="2" t="inlineStr"/>
-      <c r="BI15" s="2" t="inlineStr"/>
+      <c r="BI15" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ15" s="2" t="inlineStr"/>
-      <c r="BK15" s="2" t="inlineStr"/>
-      <c r="BL15" s="2" t="inlineStr"/>
+      <c r="BK15" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3627,28 +3830,32 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -3692,7 +3899,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -3701,7 +3908,11 @@
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr"/>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>250110d0a1034f05be428d667d6477b6</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
           <t>ce1c217c7e746a809289203e</t>
@@ -3722,7 +3933,11 @@
       <c r="AL17" s="2" t="inlineStr"/>
       <c r="AM17" s="2" t="inlineStr"/>
       <c r="AN17" s="2" t="inlineStr"/>
-      <c r="AO17" s="2" t="inlineStr"/>
+      <c r="AO17" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP17" s="2" t="inlineStr"/>
       <c r="AQ17" s="2" t="inlineStr"/>
       <c r="AR17" s="2" t="inlineStr"/>
@@ -3758,10 +3973,22 @@
         </is>
       </c>
       <c r="BH17" s="2" t="inlineStr"/>
-      <c r="BI17" s="2" t="inlineStr"/>
+      <c r="BI17" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ17" s="2" t="inlineStr"/>
-      <c r="BK17" s="2" t="inlineStr"/>
-      <c r="BL17" s="2" t="inlineStr"/>
+      <c r="BK17" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4589,28 +4816,32 @@
       <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -4654,7 +4885,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -4663,7 +4894,11 @@
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr"/>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>3e28eb7e592043efa29b6a457a0a5788</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
           <t>aba1c81f6a4f2c173c8ece68</t>
@@ -4684,7 +4919,11 @@
       <c r="AL22" s="2" t="inlineStr"/>
       <c r="AM22" s="2" t="inlineStr"/>
       <c r="AN22" s="2" t="inlineStr"/>
-      <c r="AO22" s="2" t="inlineStr"/>
+      <c r="AO22" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP22" s="2" t="inlineStr"/>
       <c r="AQ22" s="2" t="inlineStr"/>
       <c r="AR22" s="2" t="inlineStr"/>
@@ -4720,10 +4959,22 @@
         </is>
       </c>
       <c r="BH22" s="2" t="inlineStr"/>
-      <c r="BI22" s="2" t="inlineStr"/>
+      <c r="BI22" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ22" s="2" t="inlineStr"/>
-      <c r="BK22" s="2" t="inlineStr"/>
-      <c r="BL22" s="2" t="inlineStr"/>
+      <c r="BK22" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5353,28 +5604,32 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -5418,7 +5673,7 @@
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -5427,7 +5682,11 @@
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr"/>
-      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>3a4f4d0abf774aaeb3efdb0aaffd0827</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
           <t>9de229fd2c6d6b7abcb323d2</t>
@@ -5448,7 +5707,11 @@
       <c r="AL26" s="2" t="inlineStr"/>
       <c r="AM26" s="2" t="inlineStr"/>
       <c r="AN26" s="2" t="inlineStr"/>
-      <c r="AO26" s="2" t="inlineStr"/>
+      <c r="AO26" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP26" s="2" t="inlineStr"/>
       <c r="AQ26" s="2" t="inlineStr"/>
       <c r="AR26" s="2" t="inlineStr"/>
@@ -5492,10 +5755,22 @@
         </is>
       </c>
       <c r="BH26" s="2" t="inlineStr"/>
-      <c r="BI26" s="2" t="inlineStr"/>
+      <c r="BI26" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ26" s="2" t="inlineStr"/>
-      <c r="BK26" s="2" t="inlineStr"/>
-      <c r="BL26" s="2" t="inlineStr"/>
+      <c r="BK26" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -6707,28 +6982,32 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -6772,7 +7051,7 @@
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -6781,7 +7060,11 @@
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr"/>
-      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>dbf25c27099e4670bcc29fc282e55e10</t>
+        </is>
+      </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
           <t>18b917029593410bd4288ab3</t>
@@ -6802,7 +7085,11 @@
       <c r="AL33" s="2" t="inlineStr"/>
       <c r="AM33" s="2" t="inlineStr"/>
       <c r="AN33" s="2" t="inlineStr"/>
-      <c r="AO33" s="2" t="inlineStr"/>
+      <c r="AO33" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP33" s="2" t="inlineStr"/>
       <c r="AQ33" s="2" t="inlineStr"/>
       <c r="AR33" s="2" t="inlineStr"/>
@@ -6846,10 +7133,22 @@
         </is>
       </c>
       <c r="BH33" s="2" t="inlineStr"/>
-      <c r="BI33" s="2" t="inlineStr"/>
+      <c r="BI33" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ33" s="2" t="inlineStr"/>
-      <c r="BK33" s="2" t="inlineStr"/>
-      <c r="BL33" s="2" t="inlineStr"/>
+      <c r="BK33" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6885,28 +7184,32 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -6950,7 +7253,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -6959,7 +7262,11 @@
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr"/>
-      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>b5a61004ea854231965b0a3e30184314</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>4b201fb734d919746fc6c7ab</t>
@@ -6980,7 +7287,11 @@
       <c r="AL34" s="2" t="inlineStr"/>
       <c r="AM34" s="2" t="inlineStr"/>
       <c r="AN34" s="2" t="inlineStr"/>
-      <c r="AO34" s="2" t="inlineStr"/>
+      <c r="AO34" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP34" s="2" t="inlineStr"/>
       <c r="AQ34" s="2" t="inlineStr"/>
       <c r="AR34" s="2" t="inlineStr"/>
@@ -7016,10 +7327,22 @@
         </is>
       </c>
       <c r="BH34" s="2" t="inlineStr"/>
-      <c r="BI34" s="2" t="inlineStr"/>
+      <c r="BI34" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ34" s="2" t="inlineStr"/>
-      <c r="BK34" s="2" t="inlineStr"/>
-      <c r="BL34" s="2" t="inlineStr"/>
+      <c r="BK34" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7055,28 +7378,32 @@
       <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -7120,7 +7447,7 @@
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -7129,7 +7456,11 @@
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr"/>
-      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>f0d6680eba81436da35e94e49182a25a</t>
+        </is>
+      </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
           <t>eae0d603c987463b7110c040</t>
@@ -7150,7 +7481,11 @@
       <c r="AL35" s="2" t="inlineStr"/>
       <c r="AM35" s="2" t="inlineStr"/>
       <c r="AN35" s="2" t="inlineStr"/>
-      <c r="AO35" s="2" t="inlineStr"/>
+      <c r="AO35" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP35" s="2" t="inlineStr"/>
       <c r="AQ35" s="2" t="inlineStr"/>
       <c r="AR35" s="2" t="inlineStr"/>
@@ -7194,10 +7529,22 @@
         </is>
       </c>
       <c r="BH35" s="2" t="inlineStr"/>
-      <c r="BI35" s="2" t="inlineStr"/>
+      <c r="BI35" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ35" s="2" t="inlineStr"/>
-      <c r="BK35" s="2" t="inlineStr"/>
-      <c r="BL35" s="2" t="inlineStr"/>
+      <c r="BK35" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7427,28 +7774,32 @@
       <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -7492,7 +7843,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -7501,7 +7852,11 @@
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr"/>
-      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>de317a559305483fb0a500b9c9503abb</t>
+        </is>
+      </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
           <t>88bd6444374e3650cc017dff</t>
@@ -7522,7 +7877,11 @@
       <c r="AL37" s="2" t="inlineStr"/>
       <c r="AM37" s="2" t="inlineStr"/>
       <c r="AN37" s="2" t="inlineStr"/>
-      <c r="AO37" s="2" t="inlineStr"/>
+      <c r="AO37" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP37" s="2" t="inlineStr"/>
       <c r="AQ37" s="2" t="inlineStr"/>
       <c r="AR37" s="2" t="inlineStr"/>
@@ -7566,10 +7925,22 @@
         </is>
       </c>
       <c r="BH37" s="2" t="inlineStr"/>
-      <c r="BI37" s="2" t="inlineStr"/>
+      <c r="BI37" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ37" s="2" t="inlineStr"/>
-      <c r="BK37" s="2" t="inlineStr"/>
-      <c r="BL37" s="2" t="inlineStr"/>
+      <c r="BK37" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -8009,28 +8380,32 @@
       <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -8074,7 +8449,7 @@
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -8083,7 +8458,11 @@
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr"/>
-      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>1efa9133cab344f8977e1ee063ad4798</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
           <t>2b2ec40c9787f933203eadd7</t>
@@ -8104,7 +8483,11 @@
       <c r="AL40" s="2" t="inlineStr"/>
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr"/>
-      <c r="AO40" s="2" t="inlineStr"/>
+      <c r="AO40" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP40" s="2" t="inlineStr"/>
       <c r="AQ40" s="2" t="inlineStr"/>
       <c r="AR40" s="2" t="inlineStr"/>
@@ -8148,10 +8531,22 @@
         </is>
       </c>
       <c r="BH40" s="2" t="inlineStr"/>
-      <c r="BI40" s="2" t="inlineStr"/>
+      <c r="BI40" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ40" s="2" t="inlineStr"/>
-      <c r="BK40" s="2" t="inlineStr"/>
-      <c r="BL40" s="2" t="inlineStr"/>
+      <c r="BK40" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8187,28 +8582,32 @@
       <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -8252,7 +8651,7 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -8261,7 +8660,11 @@
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr"/>
-      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>51c25707bcd64bb5bd4bbaefcd0ea5c2</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
           <t>dbf6244aa905808e21c2160d</t>
@@ -8282,7 +8685,11 @@
       <c r="AL41" s="2" t="inlineStr"/>
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr"/>
-      <c r="AO41" s="2" t="inlineStr"/>
+      <c r="AO41" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP41" s="2" t="inlineStr"/>
       <c r="AQ41" s="2" t="inlineStr"/>
       <c r="AR41" s="2" t="inlineStr"/>
@@ -8326,10 +8733,22 @@
         </is>
       </c>
       <c r="BH41" s="2" t="inlineStr"/>
-      <c r="BI41" s="2" t="inlineStr"/>
+      <c r="BI41" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ41" s="2" t="inlineStr"/>
-      <c r="BK41" s="2" t="inlineStr"/>
-      <c r="BL41" s="2" t="inlineStr"/>
+      <c r="BK41" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -9335,28 +9754,32 @@
       <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -9400,7 +9823,7 @@
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -9409,7 +9832,11 @@
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr"/>
-      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>2bffb2997f0e44d1b80ec8ad408bfdb3</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
           <t>bdb5852bece203541a04c720</t>
@@ -9430,7 +9857,11 @@
       <c r="AL47" s="2" t="inlineStr"/>
       <c r="AM47" s="2" t="inlineStr"/>
       <c r="AN47" s="2" t="inlineStr"/>
-      <c r="AO47" s="2" t="inlineStr"/>
+      <c r="AO47" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP47" s="2" t="inlineStr"/>
       <c r="AQ47" s="2" t="inlineStr"/>
       <c r="AR47" s="2" t="inlineStr"/>
@@ -9474,10 +9905,22 @@
         </is>
       </c>
       <c r="BH47" s="2" t="inlineStr"/>
-      <c r="BI47" s="2" t="inlineStr"/>
+      <c r="BI47" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ47" s="2" t="inlineStr"/>
-      <c r="BK47" s="2" t="inlineStr"/>
-      <c r="BL47" s="2" t="inlineStr"/>
+      <c r="BK47" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9699,28 +10142,32 @@
       <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -9764,7 +10211,7 @@
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -9773,7 +10220,11 @@
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr"/>
-      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>1ee0b5824be84e7280612344eddbbe30</t>
+        </is>
+      </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
           <t>f6ae4c7482a47ec76f3f2600</t>
@@ -9794,7 +10245,11 @@
       <c r="AL49" s="2" t="inlineStr"/>
       <c r="AM49" s="2" t="inlineStr"/>
       <c r="AN49" s="2" t="inlineStr"/>
-      <c r="AO49" s="2" t="inlineStr"/>
+      <c r="AO49" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP49" s="2" t="inlineStr"/>
       <c r="AQ49" s="2" t="inlineStr"/>
       <c r="AR49" s="2" t="inlineStr"/>
@@ -9838,10 +10293,22 @@
         </is>
       </c>
       <c r="BH49" s="2" t="inlineStr"/>
-      <c r="BI49" s="2" t="inlineStr"/>
+      <c r="BI49" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ49" s="2" t="inlineStr"/>
-      <c r="BK49" s="2" t="inlineStr"/>
-      <c r="BL49" s="2" t="inlineStr"/>
+      <c r="BK49" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9877,28 +10344,32 @@
       <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -9942,7 +10413,7 @@
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -9951,7 +10422,11 @@
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr"/>
-      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>3a75ecc9add5407d9d36969d5ba67951</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
           <t>58d4875f125cdd0032a1e22e</t>
@@ -9972,7 +10447,11 @@
       <c r="AL50" s="2" t="inlineStr"/>
       <c r="AM50" s="2" t="inlineStr"/>
       <c r="AN50" s="2" t="inlineStr"/>
-      <c r="AO50" s="2" t="inlineStr"/>
+      <c r="AO50" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP50" s="2" t="inlineStr"/>
       <c r="AQ50" s="2" t="inlineStr"/>
       <c r="AR50" s="2" t="inlineStr"/>
@@ -10016,10 +10495,22 @@
         </is>
       </c>
       <c r="BH50" s="2" t="inlineStr"/>
-      <c r="BI50" s="2" t="inlineStr"/>
+      <c r="BI50" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ50" s="2" t="inlineStr"/>
-      <c r="BK50" s="2" t="inlineStr"/>
-      <c r="BL50" s="2" t="inlineStr"/>
+      <c r="BK50" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -10807,28 +11298,32 @@
       <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -10872,7 +11367,7 @@
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -10881,7 +11376,11 @@
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr"/>
-      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>02d8ee7033c24c32a27ffb68f9decfa4</t>
+        </is>
+      </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
           <t>213e2dd0f76a739577d1cffd</t>
@@ -10902,7 +11401,11 @@
       <c r="AL55" s="2" t="inlineStr"/>
       <c r="AM55" s="2" t="inlineStr"/>
       <c r="AN55" s="2" t="inlineStr"/>
-      <c r="AO55" s="2" t="inlineStr"/>
+      <c r="AO55" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP55" s="2" t="inlineStr"/>
       <c r="AQ55" s="2" t="inlineStr"/>
       <c r="AR55" s="2" t="inlineStr"/>
@@ -10946,10 +11449,22 @@
         </is>
       </c>
       <c r="BH55" s="2" t="inlineStr"/>
-      <c r="BI55" s="2" t="inlineStr"/>
+      <c r="BI55" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ55" s="2" t="inlineStr"/>
-      <c r="BK55" s="2" t="inlineStr"/>
-      <c r="BL55" s="2" t="inlineStr"/>
+      <c r="BK55" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL55" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10985,28 +11500,32 @@
       <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -11050,7 +11569,7 @@
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -11059,7 +11578,11 @@
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr"/>
-      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>a6692545f7eb4397afc847407066d2e4</t>
+        </is>
+      </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
           <t>48ce42f77c51b4a27079cdc5</t>
@@ -11080,7 +11603,11 @@
       <c r="AL56" s="2" t="inlineStr"/>
       <c r="AM56" s="2" t="inlineStr"/>
       <c r="AN56" s="2" t="inlineStr"/>
-      <c r="AO56" s="2" t="inlineStr"/>
+      <c r="AO56" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP56" s="2" t="inlineStr"/>
       <c r="AQ56" s="2" t="inlineStr"/>
       <c r="AR56" s="2" t="inlineStr"/>
@@ -11124,10 +11651,22 @@
         </is>
       </c>
       <c r="BH56" s="2" t="inlineStr"/>
-      <c r="BI56" s="2" t="inlineStr"/>
+      <c r="BI56" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ56" s="2" t="inlineStr"/>
-      <c r="BK56" s="2" t="inlineStr"/>
-      <c r="BL56" s="2" t="inlineStr"/>
+      <c r="BK56" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -11163,28 +11702,32 @@
       <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -11228,7 +11771,7 @@
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -11237,7 +11780,11 @@
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr"/>
-      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>4851581e14234c8aa6b0dc27f00fcdc2</t>
+        </is>
+      </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
           <t>f9b1dde7103952d58312aa31</t>
@@ -11258,7 +11805,11 @@
       <c r="AL57" s="2" t="inlineStr"/>
       <c r="AM57" s="2" t="inlineStr"/>
       <c r="AN57" s="2" t="inlineStr"/>
-      <c r="AO57" s="2" t="inlineStr"/>
+      <c r="AO57" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP57" s="2" t="inlineStr"/>
       <c r="AQ57" s="2" t="inlineStr"/>
       <c r="AR57" s="2" t="inlineStr"/>
@@ -11302,10 +11853,22 @@
         </is>
       </c>
       <c r="BH57" s="2" t="inlineStr"/>
-      <c r="BI57" s="2" t="inlineStr"/>
+      <c r="BI57" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ57" s="2" t="inlineStr"/>
-      <c r="BK57" s="2" t="inlineStr"/>
-      <c r="BL57" s="2" t="inlineStr"/>
+      <c r="BK57" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL57" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11341,28 +11904,32 @@
       <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -11406,7 +11973,7 @@
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -11415,7 +11982,11 @@
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr"/>
-      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>150cebfebdad450e94568dfce65c866c</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
           <t>783731a60955313577c7b269</t>
@@ -11436,7 +12007,11 @@
       <c r="AL58" s="2" t="inlineStr"/>
       <c r="AM58" s="2" t="inlineStr"/>
       <c r="AN58" s="2" t="inlineStr"/>
-      <c r="AO58" s="2" t="inlineStr"/>
+      <c r="AO58" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP58" s="2" t="inlineStr"/>
       <c r="AQ58" s="2" t="inlineStr"/>
       <c r="AR58" s="2" t="inlineStr"/>
@@ -11472,10 +12047,22 @@
         </is>
       </c>
       <c r="BH58" s="2" t="inlineStr"/>
-      <c r="BI58" s="2" t="inlineStr"/>
+      <c r="BI58" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ58" s="2" t="inlineStr"/>
-      <c r="BK58" s="2" t="inlineStr"/>
-      <c r="BL58" s="2" t="inlineStr"/>
+      <c r="BK58" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11511,28 +12098,32 @@
       <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>關稅</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -11576,7 +12167,7 @@
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>TARIFF</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -11585,7 +12176,11 @@
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr"/>
-      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>e0ca9b7035b9432ab9b1a8a55e29a379</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
           <t>7794017c954adb8e1d04a209</t>
@@ -11606,7 +12201,11 @@
       <c r="AL59" s="2" t="inlineStr"/>
       <c r="AM59" s="2" t="inlineStr"/>
       <c r="AN59" s="2" t="inlineStr"/>
-      <c r="AO59" s="2" t="inlineStr"/>
+      <c r="AO59" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP59" s="2" t="inlineStr"/>
       <c r="AQ59" s="2" t="inlineStr"/>
       <c r="AR59" s="2" t="inlineStr"/>
@@ -11642,10 +12241,22 @@
         </is>
       </c>
       <c r="BH59" s="2" t="inlineStr"/>
-      <c r="BI59" s="2" t="inlineStr"/>
+      <c r="BI59" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ59" s="2" t="inlineStr"/>
-      <c r="BK59" s="2" t="inlineStr"/>
-      <c r="BL59" s="2" t="inlineStr"/>
+      <c r="BK59" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL59" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11681,28 +12292,32 @@
       <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -11746,7 +12361,7 @@
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -11755,7 +12370,11 @@
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr"/>
-      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>901d67a933324db7b5183d078de1c6b8</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
           <t>0e8055e00292537850c96052</t>
@@ -11776,7 +12395,11 @@
       <c r="AL60" s="2" t="inlineStr"/>
       <c r="AM60" s="2" t="inlineStr"/>
       <c r="AN60" s="2" t="inlineStr"/>
-      <c r="AO60" s="2" t="inlineStr"/>
+      <c r="AO60" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP60" s="2" t="inlineStr"/>
       <c r="AQ60" s="2" t="inlineStr"/>
       <c r="AR60" s="2" t="inlineStr"/>
@@ -11820,10 +12443,22 @@
         </is>
       </c>
       <c r="BH60" s="2" t="inlineStr"/>
-      <c r="BI60" s="2" t="inlineStr"/>
+      <c r="BI60" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ60" s="2" t="inlineStr"/>
-      <c r="BK60" s="2" t="inlineStr"/>
-      <c r="BL60" s="2" t="inlineStr"/>
+      <c r="BK60" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11859,28 +12494,32 @@
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>產業下跌</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -11924,7 +12563,7 @@
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>SECTOR_MOVE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -11933,7 +12572,11 @@
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr"/>
-      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>48e8efe48bf44ec6b1c13472e34264d3</t>
+        </is>
+      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
           <t>5e578e62e5d9c3137dafe7b5</t>
@@ -11954,7 +12597,11 @@
       <c r="AL61" s="2" t="inlineStr"/>
       <c r="AM61" s="2" t="inlineStr"/>
       <c r="AN61" s="2" t="inlineStr"/>
-      <c r="AO61" s="2" t="inlineStr"/>
+      <c r="AO61" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP61" s="2" t="inlineStr"/>
       <c r="AQ61" s="2" t="inlineStr"/>
       <c r="AR61" s="2" t="inlineStr"/>
@@ -11998,10 +12645,22 @@
         </is>
       </c>
       <c r="BH61" s="2" t="inlineStr"/>
-      <c r="BI61" s="2" t="inlineStr"/>
+      <c r="BI61" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ61" s="2" t="inlineStr"/>
-      <c r="BK61" s="2" t="inlineStr"/>
-      <c r="BL61" s="2" t="inlineStr"/>
+      <c r="BK61" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL61" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL61"/>
